--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T09:04:56+00:00</t>
+    <t>2024-02-19T13:34:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:34:28+00:00</t>
+    <t>2024-02-19T13:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$233</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$237</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7538" uniqueCount="753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7661" uniqueCount="764">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T16:55:03+00:00</t>
+    <t>2024-03-05T15:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2079,6 +2079,42 @@
   </si>
   <si>
     <t>Organization.telecom:mailbox-mss.extension:emailType</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.url</t>
+  </si>
+  <si>
+    <t>http://interopsante.org/fhir/StructureDefinition/FrContactPointEmailType</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.value[x]</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R256-TypeMessagerie/FHIR/TRE-R256-TypeMessagerie"/&gt;
+  &lt;code value="MSSANTE"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>http://interopsante.org/fhir/ValueSet/fr-email-type</t>
   </si>
   <si>
     <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata</t>
@@ -2678,7 +2714,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ233"/>
+  <dimension ref="A1:AJ237"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="80.17578125" customWidth="true" bestFit="true"/>
@@ -24119,7 +24155,7 @@
         <v>623</v>
       </c>
       <c r="D210" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E210" s="2"/>
       <c r="F210" t="s" s="2">
@@ -24146,9 +24182,7 @@
       <c r="M210" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="N210" t="s" s="2">
-        <v>105</v>
-      </c>
+      <c r="N210" s="2"/>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
         <v>73</v>
@@ -24217,11 +24251,9 @@
         <v>664</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C211" t="s" s="2">
         <v>665</v>
       </c>
+      <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
         <v>73</v>
       </c>
@@ -24233,7 +24265,7 @@
         <v>81</v>
       </c>
       <c r="H211" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I211" t="s" s="2">
         <v>73</v>
@@ -24242,13 +24274,13 @@
         <v>73</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>666</v>
+        <v>96</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>667</v>
+        <v>97</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>668</v>
+        <v>98</v>
       </c>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
@@ -24299,27 +24331,27 @@
         <v>73</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI211" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ211" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>626</v>
+        <v>667</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -24327,10 +24359,10 @@
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G212" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H212" t="s" s="2">
         <v>73</v>
@@ -24339,20 +24371,18 @@
         <v>73</v>
       </c>
       <c r="J212" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>162</v>
+        <v>102</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>627</v>
+        <v>479</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N212" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="N212" s="2"/>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>73</v>
@@ -24362,7 +24392,7 @@
         <v>73</v>
       </c>
       <c r="S212" t="s" s="2">
-        <v>670</v>
+        <v>73</v>
       </c>
       <c r="T212" t="s" s="2">
         <v>73</v>
@@ -24377,51 +24407,51 @@
         <v>73</v>
       </c>
       <c r="X212" t="s" s="2">
-        <v>285</v>
+        <v>73</v>
       </c>
       <c r="Y212" t="s" s="2">
-        <v>629</v>
+        <v>73</v>
       </c>
       <c r="Z212" t="s" s="2">
-        <v>630</v>
+        <v>73</v>
       </c>
       <c r="AA212" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB212" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC212" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD212" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE212" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>631</v>
+        <v>109</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI212" t="s" s="2">
-        <v>632</v>
+        <v>93</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>633</v>
+        <v>669</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -24435,35 +24465,33 @@
         <v>81</v>
       </c>
       <c r="H213" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I213" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J213" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>672</v>
+        <v>205</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>635</v>
+        <v>206</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="O213" t="s" s="2">
-        <v>637</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q213" s="2"/>
       <c r="R213" t="s" s="2">
-        <v>73</v>
+        <v>670</v>
       </c>
       <c r="S213" t="s" s="2">
         <v>73</v>
@@ -24505,27 +24533,27 @@
         <v>73</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>638</v>
+        <v>209</v>
       </c>
       <c r="AG213" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AH213" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI213" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>639</v>
+        <v>672</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -24542,26 +24570,22 @@
         <v>73</v>
       </c>
       <c r="I214" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J214" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>640</v>
+        <v>213</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="N214" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="O214" t="s" s="2">
-        <v>643</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N214" s="2"/>
+      <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
         <v>73</v>
       </c>
@@ -24570,7 +24594,7 @@
         <v>73</v>
       </c>
       <c r="S214" t="s" s="2">
-        <v>73</v>
+        <v>673</v>
       </c>
       <c r="T214" t="s" s="2">
         <v>73</v>
@@ -24585,13 +24609,11 @@
         <v>73</v>
       </c>
       <c r="X214" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="Y214" t="s" s="2">
-        <v>644</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="Y214" s="2"/>
       <c r="Z214" t="s" s="2">
-        <v>645</v>
+        <v>674</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>73</v>
@@ -24609,7 +24631,7 @@
         <v>73</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>646</v>
+        <v>215</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>74</v>
@@ -24629,9 +24651,11 @@
         <v>675</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="C215" s="2"/>
+        <v>621</v>
+      </c>
+      <c r="C215" t="s" s="2">
+        <v>676</v>
+      </c>
       <c r="D215" t="s" s="2">
         <v>73</v>
       </c>
@@ -24643,26 +24667,24 @@
         <v>81</v>
       </c>
       <c r="H215" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I215" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J215" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>648</v>
+        <v>677</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>649</v>
+        <v>678</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="N215" t="s" s="2">
-        <v>651</v>
-      </c>
+        <v>679</v>
+      </c>
+      <c r="N215" s="2"/>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
         <v>73</v>
@@ -24711,27 +24733,27 @@
         <v>73</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>652</v>
+        <v>109</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH215" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI215" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>653</v>
+        <v>626</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -24739,7 +24761,7 @@
       </c>
       <c r="E216" s="2"/>
       <c r="F216" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G216" t="s" s="2">
         <v>81</v>
@@ -24754,16 +24776,16 @@
         <v>82</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>212</v>
+        <v>162</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>654</v>
+        <v>627</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>655</v>
+        <v>628</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>314</v>
+        <v>379</v>
       </c>
       <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
@@ -24774,7 +24796,7 @@
         <v>73</v>
       </c>
       <c r="S216" t="s" s="2">
-        <v>73</v>
+        <v>681</v>
       </c>
       <c r="T216" t="s" s="2">
         <v>73</v>
@@ -24789,13 +24811,13 @@
         <v>73</v>
       </c>
       <c r="X216" t="s" s="2">
-        <v>73</v>
+        <v>285</v>
       </c>
       <c r="Y216" t="s" s="2">
-        <v>73</v>
+        <v>629</v>
       </c>
       <c r="Z216" t="s" s="2">
-        <v>73</v>
+        <v>630</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>73</v>
@@ -24813,7 +24835,7 @@
         <v>73</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>656</v>
+        <v>631</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>74</v>
@@ -24822,18 +24844,18 @@
         <v>81</v>
       </c>
       <c r="AI216" t="s" s="2">
-        <v>93</v>
+        <v>632</v>
       </c>
       <c r="AJ216" t="s" s="2">
-        <v>316</v>
+        <v>94</v>
       </c>
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>677</v>
+        <v>633</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24841,10 +24863,10 @@
       </c>
       <c r="E217" s="2"/>
       <c r="F217" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G217" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H217" t="s" s="2">
         <v>82</v>
@@ -24853,22 +24875,22 @@
         <v>73</v>
       </c>
       <c r="J217" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>678</v>
+        <v>96</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>680</v>
+        <v>635</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>681</v>
+        <v>636</v>
       </c>
       <c r="O217" t="s" s="2">
-        <v>682</v>
+        <v>637</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>73</v>
@@ -24917,19 +24939,19 @@
         <v>73</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>677</v>
+        <v>638</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH217" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI217" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ217" t="s" s="2">
-        <v>683</v>
+        <v>94</v>
       </c>
     </row>
     <row r="218" hidden="true">
@@ -24937,7 +24959,7 @@
         <v>684</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>684</v>
+        <v>639</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -24954,25 +24976,25 @@
         <v>73</v>
       </c>
       <c r="I218" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J218" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K218" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L218" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="M218" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="N218" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="L218" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="M218" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="N218" t="s" s="2">
-        <v>688</v>
-      </c>
       <c r="O218" t="s" s="2">
-        <v>689</v>
+        <v>643</v>
       </c>
       <c r="P218" t="s" s="2">
         <v>73</v>
@@ -24997,13 +25019,13 @@
         <v>73</v>
       </c>
       <c r="X218" t="s" s="2">
-        <v>73</v>
+        <v>285</v>
       </c>
       <c r="Y218" t="s" s="2">
-        <v>73</v>
+        <v>644</v>
       </c>
       <c r="Z218" t="s" s="2">
-        <v>73</v>
+        <v>645</v>
       </c>
       <c r="AA218" t="s" s="2">
         <v>73</v>
@@ -25021,7 +25043,7 @@
         <v>73</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>684</v>
+        <v>646</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>74</v>
@@ -25033,15 +25055,15 @@
         <v>93</v>
       </c>
       <c r="AJ218" t="s" s="2">
-        <v>323</v>
+        <v>94</v>
       </c>
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>690</v>
+        <v>647</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -25061,18 +25083,20 @@
         <v>73</v>
       </c>
       <c r="J219" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>96</v>
+        <v>648</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>97</v>
+        <v>649</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N219" s="2"/>
+        <v>650</v>
+      </c>
+      <c r="N219" t="s" s="2">
+        <v>651</v>
+      </c>
       <c r="O219" s="2"/>
       <c r="P219" t="s" s="2">
         <v>73</v>
@@ -25121,7 +25145,7 @@
         <v>73</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>99</v>
+        <v>652</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>74</v>
@@ -25130,29 +25154,29 @@
         <v>81</v>
       </c>
       <c r="AI219" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ219" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>691</v>
+        <v>653</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E220" s="2"/>
       <c r="F220" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G220" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H220" t="s" s="2">
         <v>73</v>
@@ -25161,19 +25185,19 @@
         <v>73</v>
       </c>
       <c r="J220" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>103</v>
+        <v>654</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>104</v>
+        <v>655</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>105</v>
+        <v>314</v>
       </c>
       <c r="O220" s="2"/>
       <c r="P220" t="s" s="2">
@@ -25211,39 +25235,39 @@
         <v>73</v>
       </c>
       <c r="AB220" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC220" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD220" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE220" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>109</v>
+        <v>656</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH220" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI220" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>110</v>
+        <v>316</v>
       </c>
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -25254,30 +25278,32 @@
         <v>74</v>
       </c>
       <c r="G221" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H221" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I221" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J221" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="L221" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="M221" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N221" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="O221" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="M221" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="N221" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="O221" s="2"/>
       <c r="P221" t="s" s="2">
         <v>73</v>
       </c>
@@ -25325,27 +25351,27 @@
         <v>73</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH221" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI221" t="s" s="2">
-        <v>697</v>
+        <v>93</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>94</v>
+        <v>694</v>
       </c>
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -25368,18 +25394,20 @@
         <v>82</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>128</v>
+        <v>696</v>
       </c>
       <c r="L222" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="M222" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="N222" t="s" s="2">
         <v>699</v>
       </c>
-      <c r="M222" t="s" s="2">
+      <c r="O222" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="N222" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="O222" s="2"/>
       <c r="P222" t="s" s="2">
         <v>73</v>
       </c>
@@ -25403,13 +25431,13 @@
         <v>73</v>
       </c>
       <c r="X222" t="s" s="2">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="Y222" t="s" s="2">
-        <v>702</v>
+        <v>73</v>
       </c>
       <c r="Z222" t="s" s="2">
-        <v>474</v>
+        <v>73</v>
       </c>
       <c r="AA222" t="s" s="2">
         <v>73</v>
@@ -25427,7 +25455,7 @@
         <v>73</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>74</v>
@@ -25439,15 +25467,15 @@
         <v>93</v>
       </c>
       <c r="AJ222" t="s" s="2">
-        <v>94</v>
+        <v>323</v>
       </c>
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -25467,20 +25495,18 @@
         <v>73</v>
       </c>
       <c r="J223" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>271</v>
+        <v>96</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>705</v>
+        <v>97</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="N223" t="s" s="2">
-        <v>707</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="N223" s="2"/>
       <c r="O223" s="2"/>
       <c r="P223" t="s" s="2">
         <v>73</v>
@@ -25529,7 +25555,7 @@
         <v>73</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>708</v>
+        <v>99</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>74</v>
@@ -25538,29 +25564,29 @@
         <v>81</v>
       </c>
       <c r="AI223" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ223" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E224" s="2"/>
       <c r="F224" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G224" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H224" t="s" s="2">
         <v>73</v>
@@ -25569,19 +25595,19 @@
         <v>73</v>
       </c>
       <c r="J224" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>710</v>
+        <v>103</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>711</v>
+        <v>104</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>712</v>
+        <v>105</v>
       </c>
       <c r="O224" s="2"/>
       <c r="P224" t="s" s="2">
@@ -25619,39 +25645,39 @@
         <v>73</v>
       </c>
       <c r="AB224" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC224" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD224" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE224" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>713</v>
+        <v>109</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH224" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI224" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ224" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -25662,7 +25688,7 @@
         <v>74</v>
       </c>
       <c r="G225" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H225" t="s" s="2">
         <v>73</v>
@@ -25671,23 +25697,21 @@
         <v>73</v>
       </c>
       <c r="J225" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>715</v>
+        <v>96</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>716</v>
+        <v>704</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="N225" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="O225" t="s" s="2">
-        <v>719</v>
-      </c>
+        <v>706</v>
+      </c>
+      <c r="O225" s="2"/>
       <c r="P225" t="s" s="2">
         <v>73</v>
       </c>
@@ -25735,16 +25759,16 @@
         <v>73</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH225" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI225" t="s" s="2">
-        <v>93</v>
+        <v>708</v>
       </c>
       <c r="AJ225" t="s" s="2">
         <v>94</v>
@@ -25752,10 +25776,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -25775,18 +25799,20 @@
         <v>73</v>
       </c>
       <c r="J226" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>97</v>
+        <v>710</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N226" s="2"/>
+        <v>711</v>
+      </c>
+      <c r="N226" t="s" s="2">
+        <v>712</v>
+      </c>
       <c r="O226" s="2"/>
       <c r="P226" t="s" s="2">
         <v>73</v>
@@ -25811,13 +25837,13 @@
         <v>73</v>
       </c>
       <c r="X226" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="Y226" t="s" s="2">
-        <v>73</v>
+        <v>713</v>
       </c>
       <c r="Z226" t="s" s="2">
-        <v>73</v>
+        <v>474</v>
       </c>
       <c r="AA226" t="s" s="2">
         <v>73</v>
@@ -25835,7 +25861,7 @@
         <v>73</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>99</v>
+        <v>714</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>74</v>
@@ -25844,29 +25870,29 @@
         <v>81</v>
       </c>
       <c r="AI226" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ226" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E227" s="2"/>
       <c r="F227" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G227" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H227" t="s" s="2">
         <v>73</v>
@@ -25875,19 +25901,19 @@
         <v>73</v>
       </c>
       <c r="J227" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>102</v>
+        <v>271</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>103</v>
+        <v>716</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>104</v>
+        <v>717</v>
       </c>
       <c r="N227" t="s" s="2">
-        <v>105</v>
+        <v>718</v>
       </c>
       <c r="O227" s="2"/>
       <c r="P227" t="s" s="2">
@@ -25925,75 +25951,73 @@
         <v>73</v>
       </c>
       <c r="AB227" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC227" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD227" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE227" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>109</v>
+        <v>719</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH227" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI227" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ227" t="s" s="2">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
-        <v>723</v>
+        <v>73</v>
       </c>
       <c r="E228" s="2"/>
       <c r="F228" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G228" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H228" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I228" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J228" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O228" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>723</v>
+      </c>
+      <c r="O228" s="2"/>
       <c r="P228" t="s" s="2">
         <v>73</v>
       </c>
@@ -26041,27 +26065,27 @@
         <v>73</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH228" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI228" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ228" t="s" s="2">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -26072,7 +26096,7 @@
         <v>74</v>
       </c>
       <c r="G229" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H229" t="s" s="2">
         <v>73</v>
@@ -26084,19 +26108,19 @@
         <v>73</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>290</v>
+        <v>726</v>
       </c>
       <c r="L229" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="M229" t="s" s="2">
         <v>728</v>
       </c>
-      <c r="M229" t="s" s="2">
+      <c r="N229" t="s" s="2">
         <v>729</v>
       </c>
-      <c r="N229" t="s" s="2">
+      <c r="O229" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="O229" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="P229" t="s" s="2">
         <v>73</v>
@@ -26121,13 +26145,13 @@
         <v>73</v>
       </c>
       <c r="X229" t="s" s="2">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="Y229" t="s" s="2">
-        <v>732</v>
+        <v>73</v>
       </c>
       <c r="Z229" t="s" s="2">
-        <v>733</v>
+        <v>73</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>73</v>
@@ -26145,13 +26169,13 @@
         <v>73</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH229" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI229" t="s" s="2">
         <v>93</v>
@@ -26162,10 +26186,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -26188,20 +26212,16 @@
         <v>73</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>735</v>
+        <v>96</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>736</v>
+        <v>97</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="N230" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="O230" t="s" s="2">
-        <v>739</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="N230" s="2"/>
+      <c r="O230" s="2"/>
       <c r="P230" t="s" s="2">
         <v>73</v>
       </c>
@@ -26249,7 +26269,7 @@
         <v>73</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>734</v>
+        <v>99</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>74</v>
@@ -26258,22 +26278,22 @@
         <v>81</v>
       </c>
       <c r="AI230" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ230" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E231" s="2"/>
       <c r="F231" t="s" s="2">
@@ -26292,18 +26312,18 @@
         <v>73</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>612</v>
+        <v>102</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>741</v>
+        <v>103</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="N231" s="2"/>
-      <c r="O231" t="s" s="2">
-        <v>742</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N231" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="O231" s="2"/>
       <c r="P231" t="s" s="2">
         <v>73</v>
       </c>
@@ -26339,19 +26359,19 @@
         <v>73</v>
       </c>
       <c r="AB231" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC231" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD231" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE231" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>740</v>
+        <v>109</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>74</v>
@@ -26363,50 +26383,50 @@
         <v>93</v>
       </c>
       <c r="AJ231" t="s" s="2">
-        <v>743</v>
+        <v>110</v>
       </c>
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
-        <v>73</v>
+        <v>734</v>
       </c>
       <c r="E232" s="2"/>
       <c r="F232" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G232" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H232" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I232" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J232" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>745</v>
+        <v>102</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>680</v>
+        <v>736</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>681</v>
+        <v>105</v>
       </c>
       <c r="O232" t="s" s="2">
-        <v>747</v>
+        <v>268</v>
       </c>
       <c r="P232" t="s" s="2">
         <v>73</v>
@@ -26455,27 +26475,27 @@
         <v>73</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH232" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI232" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ232" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -26486,10 +26506,10 @@
         <v>74</v>
       </c>
       <c r="G233" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H233" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I233" t="s" s="2">
         <v>73</v>
@@ -26498,19 +26518,19 @@
         <v>73</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>749</v>
+        <v>290</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="N233" t="s" s="2">
-        <v>688</v>
+        <v>741</v>
       </c>
       <c r="O233" t="s" s="2">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>73</v>
@@ -26535,13 +26555,13 @@
         <v>73</v>
       </c>
       <c r="X233" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="Y233" t="s" s="2">
-        <v>73</v>
+        <v>743</v>
       </c>
       <c r="Z233" t="s" s="2">
-        <v>73</v>
+        <v>744</v>
       </c>
       <c r="AA233" t="s" s="2">
         <v>73</v>
@@ -26559,23 +26579,437 @@
         <v>73</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH233" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI233" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ233" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="234" hidden="true">
+      <c r="A234" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="B234" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="C234" s="2"/>
+      <c r="D234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E234" s="2"/>
+      <c r="F234" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G234" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K234" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="L234" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="M234" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="N234" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="O234" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="P234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q234" s="2"/>
+      <c r="R234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF234" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="AG234" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH234" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI234" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ234" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="235" hidden="true">
+      <c r="A235" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="B235" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="C235" s="2"/>
+      <c r="D235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E235" s="2"/>
+      <c r="F235" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G235" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K235" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="L235" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="M235" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="N235" s="2"/>
+      <c r="O235" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="P235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q235" s="2"/>
+      <c r="R235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF235" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="AG235" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH235" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI235" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ235" t="s" s="2">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="236" hidden="true">
+      <c r="A236" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="B236" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="C236" s="2"/>
+      <c r="D236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E236" s="2"/>
+      <c r="F236" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G236" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K236" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="L236" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="M236" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N236" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="O236" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="P236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q236" s="2"/>
+      <c r="R236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF236" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="AG236" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH236" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI236" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ236" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="237" hidden="true">
+      <c r="A237" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="B237" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="C237" s="2"/>
+      <c r="D237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E237" s="2"/>
+      <c r="F237" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K237" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="L237" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="M237" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="N237" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="O237" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="P237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q237" s="2"/>
+      <c r="R237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF237" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="AG237" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI237" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ237" t="s" s="2">
         <v>323</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ233">
+  <autoFilter ref="A1:AJ237">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -26585,7 +27019,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI232">
+  <conditionalFormatting sqref="A2:AI236">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T15:34:40+00:00</t>
+    <t>2024-03-06T10:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$237</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$224</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7661" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7248" uniqueCount="737">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T10:45:14+00:00</t>
+    <t>2024-03-07T10:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2070,91 +2070,6 @@
   </si>
   <si>
     <t>Les BALs MSS de type ORG ou APP rattachées à une personne morale responsable de l’accès et de l’usage de la BAL (boiteLettreMSS).</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType.url</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.url</t>
-  </si>
-  <si>
-    <t>http://interopsante.org/fhir/StructureDefinition/FrContactPointEmailType</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.value[x]</t>
-  </si>
-  <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R256-TypeMessagerie/FHIR/TRE-R256-TypeMessagerie"/&gt;
-  &lt;code value="MSSANTE"/&gt;
-&lt;/valueCoding&gt;</t>
-  </si>
-  <si>
-    <t>http://interopsante.org/fhir/ValueSet/fr-email-type</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t>as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata}
-</t>
-  </si>
-  <si>
-    <t>Les attributs 'responsible' et 'phone' ne sont pas disponibles en accès libre.</t>
-  </si>
-  <si>
-    <t>Extension contenant les métadonnées de la mailbox mss.</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.system</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.value</t>
-  </si>
-  <si>
-    <t>Boîte Aux Lettres (BAL) MSS</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.use</t>
-  </si>
-  <si>
-    <t>Applications can assume that a contact is current unless it explicitly says that it is temporary or old.</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.rank</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.period</t>
   </si>
   <si>
     <t>Organization.address</t>
@@ -2714,7 +2629,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ237"/>
+  <dimension ref="A1:AJ224"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="80.17578125" customWidth="true" bestFit="true"/>
@@ -23947,7 +23862,7 @@
         <v>661</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>620</v>
+        <v>661</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -23958,10 +23873,10 @@
         <v>74</v>
       </c>
       <c r="G208" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H208" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I208" t="s" s="2">
         <v>73</v>
@@ -23970,16 +23885,20 @@
         <v>73</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>96</v>
+        <v>662</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>97</v>
+        <v>663</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N208" s="2"/>
-      <c r="O208" s="2"/>
+        <v>664</v>
+      </c>
+      <c r="N208" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="O208" t="s" s="2">
+        <v>666</v>
+      </c>
       <c r="P208" t="s" s="2">
         <v>73</v>
       </c>
@@ -24027,38 +23946,38 @@
         <v>73</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>99</v>
+        <v>661</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH208" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI208" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>73</v>
+        <v>667</v>
       </c>
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>621</v>
+        <v>668</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H209" t="s" s="2">
         <v>73</v>
@@ -24067,21 +23986,23 @@
         <v>73</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>102</v>
+        <v>669</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>103</v>
+        <v>670</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>104</v>
+        <v>671</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O209" s="2"/>
+        <v>672</v>
+      </c>
+      <c r="O209" t="s" s="2">
+        <v>673</v>
+      </c>
       <c r="P209" t="s" s="2">
         <v>73</v>
       </c>
@@ -24117,43 +24038,41 @@
         <v>73</v>
       </c>
       <c r="AB209" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC209" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD209" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE209" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>109</v>
+        <v>668</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH209" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI209" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>110</v>
+        <v>323</v>
       </c>
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C210" t="s" s="2">
-        <v>623</v>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
         <v>73</v>
       </c>
@@ -24174,13 +24093,13 @@
         <v>73</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>624</v>
+        <v>96</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>625</v>
+        <v>97</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>191</v>
+        <v>98</v>
       </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
@@ -24231,38 +24150,38 @@
         <v>73</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH210" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI210" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>73</v>
@@ -24274,15 +24193,17 @@
         <v>73</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N211" s="2"/>
+        <v>104</v>
+      </c>
+      <c r="N211" t="s" s="2">
+        <v>105</v>
+      </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
         <v>73</v>
@@ -24319,39 +24240,39 @@
         <v>73</v>
       </c>
       <c r="AB211" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC211" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD211" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE211" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI211" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ211" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -24362,7 +24283,7 @@
         <v>74</v>
       </c>
       <c r="G212" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H212" t="s" s="2">
         <v>73</v>
@@ -24371,18 +24292,20 @@
         <v>73</v>
       </c>
       <c r="J212" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>479</v>
+        <v>677</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N212" s="2"/>
+        <v>678</v>
+      </c>
+      <c r="N212" t="s" s="2">
+        <v>679</v>
+      </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>73</v>
@@ -24419,39 +24342,39 @@
         <v>73</v>
       </c>
       <c r="AB212" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC212" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD212" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE212" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>109</v>
+        <v>680</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI212" t="s" s="2">
-        <v>93</v>
+        <v>681</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>668</v>
+        <v>682</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>669</v>
+        <v>682</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -24459,7 +24382,7 @@
       </c>
       <c r="E213" s="2"/>
       <c r="F213" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G213" t="s" s="2">
         <v>81</v>
@@ -24471,19 +24394,19 @@
         <v>73</v>
       </c>
       <c r="J213" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K213" t="s" s="2">
         <v>128</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>205</v>
+        <v>683</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>206</v>
+        <v>684</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>207</v>
+        <v>685</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
@@ -24491,7 +24414,7 @@
       </c>
       <c r="Q213" s="2"/>
       <c r="R213" t="s" s="2">
-        <v>670</v>
+        <v>73</v>
       </c>
       <c r="S213" t="s" s="2">
         <v>73</v>
@@ -24509,13 +24432,13 @@
         <v>73</v>
       </c>
       <c r="X213" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>73</v>
+        <v>686</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>73</v>
+        <v>474</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>73</v>
@@ -24533,27 +24456,27 @@
         <v>73</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>209</v>
+        <v>687</v>
       </c>
       <c r="AG213" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AH213" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI213" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>671</v>
+        <v>688</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>672</v>
+        <v>688</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -24573,18 +24496,20 @@
         <v>73</v>
       </c>
       <c r="J214" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>140</v>
+        <v>271</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>213</v>
+        <v>689</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N214" s="2"/>
+        <v>690</v>
+      </c>
+      <c r="N214" t="s" s="2">
+        <v>691</v>
+      </c>
       <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
         <v>73</v>
@@ -24594,7 +24519,7 @@
         <v>73</v>
       </c>
       <c r="S214" t="s" s="2">
-        <v>673</v>
+        <v>73</v>
       </c>
       <c r="T214" t="s" s="2">
         <v>73</v>
@@ -24609,11 +24534,13 @@
         <v>73</v>
       </c>
       <c r="X214" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y214" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Y214" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="Z214" t="s" s="2">
-        <v>674</v>
+        <v>73</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>73</v>
@@ -24631,7 +24558,7 @@
         <v>73</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>215</v>
+        <v>692</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>74</v>
@@ -24648,14 +24575,12 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C215" t="s" s="2">
-        <v>676</v>
-      </c>
+        <v>693</v>
+      </c>
+      <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
         <v>73</v>
       </c>
@@ -24667,24 +24592,26 @@
         <v>81</v>
       </c>
       <c r="H215" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I215" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J215" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I215" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J215" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K215" t="s" s="2">
-        <v>677</v>
+        <v>96</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>678</v>
+        <v>694</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="N215" s="2"/>
+        <v>695</v>
+      </c>
+      <c r="N215" t="s" s="2">
+        <v>696</v>
+      </c>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
         <v>73</v>
@@ -24733,27 +24660,27 @@
         <v>73</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>109</v>
+        <v>697</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH215" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI215" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>680</v>
+        <v>698</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>626</v>
+        <v>698</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -24761,10 +24688,10 @@
       </c>
       <c r="E216" s="2"/>
       <c r="F216" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H216" t="s" s="2">
         <v>73</v>
@@ -24773,21 +24700,23 @@
         <v>73</v>
       </c>
       <c r="J216" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>162</v>
+        <v>699</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>627</v>
+        <v>700</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>628</v>
+        <v>701</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O216" s="2"/>
+        <v>702</v>
+      </c>
+      <c r="O216" t="s" s="2">
+        <v>703</v>
+      </c>
       <c r="P216" t="s" s="2">
         <v>73</v>
       </c>
@@ -24796,7 +24725,7 @@
         <v>73</v>
       </c>
       <c r="S216" t="s" s="2">
-        <v>681</v>
+        <v>73</v>
       </c>
       <c r="T216" t="s" s="2">
         <v>73</v>
@@ -24811,13 +24740,13 @@
         <v>73</v>
       </c>
       <c r="X216" t="s" s="2">
-        <v>285</v>
+        <v>73</v>
       </c>
       <c r="Y216" t="s" s="2">
-        <v>629</v>
+        <v>73</v>
       </c>
       <c r="Z216" t="s" s="2">
-        <v>630</v>
+        <v>73</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>73</v>
@@ -24835,16 +24764,16 @@
         <v>73</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>631</v>
+        <v>698</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH216" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI216" t="s" s="2">
-        <v>632</v>
+        <v>93</v>
       </c>
       <c r="AJ216" t="s" s="2">
         <v>94</v>
@@ -24852,10 +24781,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>682</v>
+        <v>704</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>633</v>
+        <v>704</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24863,35 +24792,31 @@
       </c>
       <c r="E217" s="2"/>
       <c r="F217" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G217" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H217" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I217" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J217" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K217" t="s" s="2">
         <v>96</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>683</v>
+        <v>97</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="N217" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="O217" t="s" s="2">
-        <v>637</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="N217" s="2"/>
+      <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
         <v>73</v>
       </c>
@@ -24939,7 +24864,7 @@
         <v>73</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>638</v>
+        <v>99</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>74</v>
@@ -24948,54 +24873,52 @@
         <v>81</v>
       </c>
       <c r="AI217" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ217" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>684</v>
+        <v>705</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>639</v>
+        <v>705</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E218" s="2"/>
       <c r="F218" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G218" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H218" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I218" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J218" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>162</v>
+        <v>102</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>640</v>
+        <v>103</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>641</v>
+        <v>104</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="O218" t="s" s="2">
-        <v>643</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="O218" s="2"/>
       <c r="P218" t="s" s="2">
         <v>73</v>
       </c>
@@ -25019,85 +24942,87 @@
         <v>73</v>
       </c>
       <c r="X218" t="s" s="2">
-        <v>285</v>
+        <v>73</v>
       </c>
       <c r="Y218" t="s" s="2">
-        <v>644</v>
+        <v>73</v>
       </c>
       <c r="Z218" t="s" s="2">
-        <v>645</v>
+        <v>73</v>
       </c>
       <c r="AA218" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB218" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC218" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD218" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE218" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>646</v>
+        <v>109</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH218" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI218" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ218" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>686</v>
+        <v>706</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>647</v>
+        <v>706</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
-        <v>73</v>
+        <v>707</v>
       </c>
       <c r="E219" s="2"/>
       <c r="F219" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G219" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H219" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I219" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J219" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>648</v>
+        <v>102</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>649</v>
+        <v>708</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>650</v>
+        <v>709</v>
       </c>
       <c r="N219" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="O219" s="2"/>
+        <v>105</v>
+      </c>
+      <c r="O219" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="P219" t="s" s="2">
         <v>73</v>
       </c>
@@ -25145,27 +25070,27 @@
         <v>73</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>652</v>
+        <v>710</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH219" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI219" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ219" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>687</v>
+        <v>711</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>653</v>
+        <v>711</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -25185,21 +25110,23 @@
         <v>73</v>
       </c>
       <c r="J220" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>212</v>
+        <v>290</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>654</v>
+        <v>712</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>655</v>
+        <v>713</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O220" s="2"/>
+        <v>714</v>
+      </c>
+      <c r="O220" t="s" s="2">
+        <v>715</v>
+      </c>
       <c r="P220" t="s" s="2">
         <v>73</v>
       </c>
@@ -25223,13 +25150,13 @@
         <v>73</v>
       </c>
       <c r="X220" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="Y220" t="s" s="2">
-        <v>73</v>
+        <v>716</v>
       </c>
       <c r="Z220" t="s" s="2">
-        <v>73</v>
+        <v>717</v>
       </c>
       <c r="AA220" t="s" s="2">
         <v>73</v>
@@ -25247,7 +25174,7 @@
         <v>73</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>656</v>
+        <v>711</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>74</v>
@@ -25259,15 +25186,15 @@
         <v>93</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>316</v>
+        <v>94</v>
       </c>
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>688</v>
+        <v>718</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>688</v>
+        <v>718</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -25278,10 +25205,10 @@
         <v>74</v>
       </c>
       <c r="G221" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H221" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I221" t="s" s="2">
         <v>73</v>
@@ -25290,19 +25217,19 @@
         <v>73</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>689</v>
+        <v>719</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>690</v>
+        <v>720</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>691</v>
+        <v>721</v>
       </c>
       <c r="N221" t="s" s="2">
-        <v>692</v>
+        <v>722</v>
       </c>
       <c r="O221" t="s" s="2">
-        <v>693</v>
+        <v>723</v>
       </c>
       <c r="P221" t="s" s="2">
         <v>73</v>
@@ -25351,27 +25278,27 @@
         <v>73</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>688</v>
+        <v>718</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH221" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI221" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>694</v>
+        <v>94</v>
       </c>
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -25382,7 +25309,7 @@
         <v>74</v>
       </c>
       <c r="G222" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H222" t="s" s="2">
         <v>73</v>
@@ -25391,22 +25318,20 @@
         <v>73</v>
       </c>
       <c r="J222" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>696</v>
+        <v>612</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>697</v>
+        <v>725</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="N222" t="s" s="2">
-        <v>699</v>
-      </c>
+        <v>614</v>
+      </c>
+      <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>700</v>
+        <v>726</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>73</v>
@@ -25455,27 +25380,27 @@
         <v>73</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH222" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI222" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ222" t="s" s="2">
-        <v>323</v>
+        <v>727</v>
       </c>
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>701</v>
+        <v>728</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>701</v>
+        <v>728</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -25498,16 +25423,20 @@
         <v>73</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>96</v>
+        <v>729</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>97</v>
+        <v>730</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N223" s="2"/>
-      <c r="O223" s="2"/>
+        <v>664</v>
+      </c>
+      <c r="N223" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="O223" t="s" s="2">
+        <v>731</v>
+      </c>
       <c r="P223" t="s" s="2">
         <v>73</v>
       </c>
@@ -25555,7 +25484,7 @@
         <v>73</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>99</v>
+        <v>728</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>74</v>
@@ -25564,22 +25493,22 @@
         <v>81</v>
       </c>
       <c r="AI223" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ223" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>702</v>
+        <v>732</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>702</v>
+        <v>732</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E224" s="2"/>
       <c r="F224" t="s" s="2">
@@ -25589,7 +25518,7 @@
         <v>75</v>
       </c>
       <c r="H224" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I224" t="s" s="2">
         <v>73</v>
@@ -25598,18 +25527,20 @@
         <v>73</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>102</v>
+        <v>733</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>103</v>
+        <v>734</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>104</v>
+        <v>735</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O224" s="2"/>
+        <v>672</v>
+      </c>
+      <c r="O224" t="s" s="2">
+        <v>736</v>
+      </c>
       <c r="P224" t="s" s="2">
         <v>73</v>
       </c>
@@ -25645,19 +25576,19 @@
         <v>73</v>
       </c>
       <c r="AB224" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC224" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD224" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE224" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>109</v>
+        <v>732</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>74</v>
@@ -25669,1347 +25600,11 @@
         <v>93</v>
       </c>
       <c r="AJ224" t="s" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="225" hidden="true">
-      <c r="A225" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="B225" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="C225" s="2"/>
-      <c r="D225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E225" s="2"/>
-      <c r="F225" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G225" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J225" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K225" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L225" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="M225" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="N225" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="O225" s="2"/>
-      <c r="P225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q225" s="2"/>
-      <c r="R225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF225" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="AG225" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH225" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI225" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="AJ225" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="226" hidden="true">
-      <c r="A226" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="B226" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="C226" s="2"/>
-      <c r="D226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E226" s="2"/>
-      <c r="F226" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G226" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J226" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K226" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="L226" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="M226" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="N226" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="O226" s="2"/>
-      <c r="P226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q226" s="2"/>
-      <c r="R226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X226" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y226" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="Z226" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AA226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF226" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="AG226" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH226" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI226" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ226" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="227" hidden="true">
-      <c r="A227" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="B227" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="C227" s="2"/>
-      <c r="D227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E227" s="2"/>
-      <c r="F227" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G227" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J227" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K227" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="L227" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="M227" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="N227" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="O227" s="2"/>
-      <c r="P227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q227" s="2"/>
-      <c r="R227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF227" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="AG227" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH227" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI227" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ227" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="228" hidden="true">
-      <c r="A228" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="B228" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="C228" s="2"/>
-      <c r="D228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E228" s="2"/>
-      <c r="F228" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G228" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J228" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K228" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L228" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="M228" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="N228" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="O228" s="2"/>
-      <c r="P228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q228" s="2"/>
-      <c r="R228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF228" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="AG228" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH228" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI228" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ228" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="229" hidden="true">
-      <c r="A229" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="B229" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="C229" s="2"/>
-      <c r="D229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E229" s="2"/>
-      <c r="F229" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G229" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K229" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="L229" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="M229" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="N229" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="O229" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="P229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q229" s="2"/>
-      <c r="R229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF229" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="AG229" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH229" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI229" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ229" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="230" hidden="true">
-      <c r="A230" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="B230" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="C230" s="2"/>
-      <c r="D230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E230" s="2"/>
-      <c r="F230" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G230" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K230" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L230" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="M230" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N230" s="2"/>
-      <c r="O230" s="2"/>
-      <c r="P230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q230" s="2"/>
-      <c r="R230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF230" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AG230" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH230" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ230" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="231" hidden="true">
-      <c r="A231" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="B231" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="C231" s="2"/>
-      <c r="D231" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="E231" s="2"/>
-      <c r="F231" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G231" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K231" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L231" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="M231" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N231" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O231" s="2"/>
-      <c r="P231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q231" s="2"/>
-      <c r="R231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB231" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AC231" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AD231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE231" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AF231" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG231" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH231" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI231" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ231" t="s" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="232" hidden="true">
-      <c r="A232" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="B232" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="C232" s="2"/>
-      <c r="D232" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="E232" s="2"/>
-      <c r="F232" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G232" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I232" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J232" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K232" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L232" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="M232" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="N232" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O232" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="P232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q232" s="2"/>
-      <c r="R232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF232" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="AG232" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH232" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI232" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ232" t="s" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="233" hidden="true">
-      <c r="A233" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="B233" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="C233" s="2"/>
-      <c r="D233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E233" s="2"/>
-      <c r="F233" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G233" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K233" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="L233" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="M233" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="N233" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="O233" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="P233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q233" s="2"/>
-      <c r="R233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X233" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y233" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="Z233" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="AA233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF233" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="AG233" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH233" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI233" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ233" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="234" hidden="true">
-      <c r="A234" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="B234" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="C234" s="2"/>
-      <c r="D234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E234" s="2"/>
-      <c r="F234" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G234" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K234" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="L234" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="M234" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="N234" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="O234" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="P234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q234" s="2"/>
-      <c r="R234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF234" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="AG234" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH234" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI234" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ234" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="235" hidden="true">
-      <c r="A235" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="B235" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="C235" s="2"/>
-      <c r="D235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E235" s="2"/>
-      <c r="F235" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G235" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K235" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="L235" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="M235" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="N235" s="2"/>
-      <c r="O235" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="P235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q235" s="2"/>
-      <c r="R235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF235" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="AG235" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH235" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI235" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ235" t="s" s="2">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="236" hidden="true">
-      <c r="A236" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="B236" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="C236" s="2"/>
-      <c r="D236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E236" s="2"/>
-      <c r="F236" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G236" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K236" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="L236" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="M236" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="N236" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="O236" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="P236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q236" s="2"/>
-      <c r="R236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF236" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="AG236" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH236" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI236" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ236" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="237" hidden="true">
-      <c r="A237" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="B237" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="C237" s="2"/>
-      <c r="D237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E237" s="2"/>
-      <c r="F237" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G237" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H237" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K237" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="L237" t="s" s="2">
-        <v>761</v>
-      </c>
-      <c r="M237" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="N237" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="O237" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="P237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q237" s="2"/>
-      <c r="R237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF237" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="AG237" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH237" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI237" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ237" t="s" s="2">
         <v>323</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ237">
+  <autoFilter ref="A1:AJ224">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -27019,7 +25614,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI236">
+  <conditionalFormatting sqref="A2:AI223">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T10:27:01+00:00</t>
+    <t>2024-03-12T12:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T12:54:34+00:00</t>
+    <t>2024-03-12T13:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:20:54+00:00</t>
+    <t>2024-03-12T13:39:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:39:01+00:00</t>
+    <t>2024-03-12T13:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:58:30+00:00</t>
+    <t>2024-03-12T14:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:02:45+00:00</t>
+    <t>2024-03-12T14:08:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:08:02+00:00</t>
+    <t>2024-03-12T14:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:13:18+00:00</t>
+    <t>2024-03-12T14:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:29:58+00:00</t>
+    <t>2024-03-12T16:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T16:57:02+00:00</t>
+    <t>2024-03-12T17:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T17:28:16+00:00</t>
+    <t>2024-03-13T08:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T08:21:45+00:00</t>
+    <t>2024-03-13T15:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:21:15+00:00</t>
+    <t>2024-03-13T15:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:40:01+00:00</t>
+    <t>2024-03-15T14:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T13:53:07+00:00</t>
+    <t>2024-04-02T14:01:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-4</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:01:28+00:00</t>
+    <t>2024-04-03T13:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:41:20+00:00</t>
+    <t>2024-04-08T12:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8294" uniqueCount="830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8295" uniqueCount="830">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-09T07:46:55+00:00</t>
+    <t>2024-04-10T12:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -692,6 +692,9 @@
 </t>
   </si>
   <si>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
     <t>The date range that this organization should be considered available.</t>
   </si>
   <si>
@@ -741,7 +744,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -781,8 +784,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>dateCreation</t>
@@ -1758,9 +1761,6 @@
   </si>
   <si>
     <t>Organization.type.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-organization-types</t>
@@ -5504,10 +5504,10 @@
         <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5582,7 +5582,7 @@
         <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>79</v>
@@ -5593,10 +5593,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5711,14 +5711,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5740,12 +5740,14 @@
         <v>112</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>201</v>
+        <v>113</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -5803,7 +5805,7 @@
         <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>120</v>
@@ -5818,7 +5820,7 @@
         <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -5829,10 +5831,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5858,13 +5860,13 @@
         <v>138</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5872,7 +5874,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>79</v>
@@ -5914,7 +5916,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>91</v>
@@ -5949,10 +5951,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5975,13 +5977,13 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -6032,7 +6034,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -6041,7 +6043,7 @@
         <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>103</v>
@@ -6067,10 +6069,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6185,10 +6187,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6279,7 +6281,7 @@
         <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>120</v>
@@ -6294,7 +6296,7 @@
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -6305,10 +6307,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6331,16 +6333,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6390,7 +6392,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -6399,22 +6401,22 @@
         <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -6425,10 +6427,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6451,23 +6453,23 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="R30" t="s" s="2">
         <v>79</v>
@@ -6512,7 +6514,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6521,22 +6523,22 @@
         <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -6547,13 +6549,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>79</v>
@@ -6575,13 +6577,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6667,13 +6669,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>79</v>
@@ -6695,13 +6697,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6767,7 +6769,7 @@
         <v>120</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>79</v>
@@ -6787,13 +6789,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>79</v>
@@ -6815,13 +6817,13 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6890,7 +6892,7 @@
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
@@ -6907,13 +6909,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>79</v>
@@ -6935,13 +6937,13 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -7007,10 +7009,10 @@
         <v>120</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
@@ -7027,13 +7029,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>79</v>
@@ -7055,13 +7057,13 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -7130,7 +7132,7 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
@@ -7147,13 +7149,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>79</v>
@@ -7175,13 +7177,13 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -7267,10 +7269,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7296,16 +7298,16 @@
         <v>112</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -7354,7 +7356,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -7389,10 +7391,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7415,17 +7417,17 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -7462,10 +7464,10 @@
         <v>79</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>79</v>
@@ -7474,7 +7476,7 @@
         <v>118</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7483,7 +7485,7 @@
         <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>103</v>
@@ -7495,27 +7497,27 @@
         <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>79</v>
@@ -7537,17 +7539,17 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -7596,7 +7598,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7605,36 +7607,36 @@
         <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7749,10 +7751,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7869,10 +7871,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7898,16 +7900,16 @@
         <v>176</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -7917,7 +7919,7 @@
         <v>79</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>79</v>
@@ -7932,13 +7934,13 @@
         <v>79</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>79</v>
@@ -7956,7 +7958,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7980,7 +7982,7 @@
         <v>199</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -7991,10 +7993,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8017,19 +8019,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -8039,7 +8041,7 @@
         <v>79</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>79</v>
@@ -8057,10 +8059,10 @@
         <v>158</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -8078,7 +8080,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -8099,10 +8101,10 @@
         <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -8113,10 +8115,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8142,16 +8144,16 @@
         <v>138</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -8161,10 +8163,10 @@
         <v>79</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>79</v>
@@ -8200,7 +8202,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -8221,13 +8223,13 @@
         <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -8235,10 +8237,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8264,13 +8266,13 @@
         <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8284,7 +8286,7 @@
         <v>79</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>79</v>
@@ -8320,7 +8322,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -8341,13 +8343,13 @@
         <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>79</v>
@@ -8355,10 +8357,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8381,13 +8383,13 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8438,7 +8440,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8459,13 +8461,13 @@
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>79</v>
@@ -8473,10 +8475,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8499,16 +8501,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8558,7 +8560,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8579,13 +8581,13 @@
         <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>79</v>
@@ -8593,13 +8595,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>79</v>
@@ -8621,17 +8623,17 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -8680,7 +8682,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8689,36 +8691,36 @@
         <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8833,10 +8835,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8953,10 +8955,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8982,16 +8984,16 @@
         <v>176</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -9016,13 +9018,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -9040,7 +9042,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -9064,7 +9066,7 @@
         <v>199</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -9075,10 +9077,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9101,19 +9103,19 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -9141,10 +9143,10 @@
         <v>158</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -9162,7 +9164,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -9183,10 +9185,10 @@
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -9197,10 +9199,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9315,10 +9317,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9435,10 +9437,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9464,16 +9466,16 @@
         <v>154</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -9522,7 +9524,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9543,10 +9545,10 @@
         <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -9557,10 +9559,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9675,10 +9677,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9795,10 +9797,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9824,16 +9826,16 @@
         <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -9843,7 +9845,7 @@
         <v>79</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>79</v>
@@ -9882,7 +9884,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9903,10 +9905,10 @@
         <v>79</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -9917,10 +9919,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9946,13 +9948,13 @@
         <v>105</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10002,7 +10004,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -10023,10 +10025,10 @@
         <v>79</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -10037,10 +10039,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10066,14 +10068,14 @@
         <v>176</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -10122,7 +10124,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -10143,10 +10145,10 @@
         <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -10157,10 +10159,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10186,14 +10188,14 @@
         <v>105</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -10242,7 +10244,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -10263,10 +10265,10 @@
         <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -10277,10 +10279,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10303,19 +10305,19 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
@@ -10364,7 +10366,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10385,10 +10387,10 @@
         <v>79</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -10399,10 +10401,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10428,16 +10430,16 @@
         <v>105</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -10486,7 +10488,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10507,10 +10509,10 @@
         <v>79</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -10521,10 +10523,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10550,16 +10552,16 @@
         <v>138</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -10569,10 +10571,10 @@
         <v>79</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>79</v>
@@ -10608,7 +10610,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10629,13 +10631,13 @@
         <v>79</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>79</v>
@@ -10643,10 +10645,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10672,13 +10674,13 @@
         <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10692,7 +10694,7 @@
         <v>79</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>79</v>
@@ -10728,7 +10730,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10749,13 +10751,13 @@
         <v>79</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>79</v>
@@ -10763,10 +10765,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10789,13 +10791,13 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10846,7 +10848,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10867,13 +10869,13 @@
         <v>79</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>79</v>
@@ -10881,10 +10883,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10907,16 +10909,16 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10966,7 +10968,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10987,13 +10989,13 @@
         <v>79</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>79</v>
@@ -11001,13 +11003,13 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>79</v>
@@ -11029,17 +11031,17 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -11088,7 +11090,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -11097,36 +11099,36 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11241,10 +11243,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11361,10 +11363,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11390,16 +11392,16 @@
         <v>176</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -11424,13 +11426,13 @@
         <v>79</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>79</v>
@@ -11448,7 +11450,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11472,7 +11474,7 @@
         <v>199</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -11483,10 +11485,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11509,19 +11511,19 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
@@ -11549,10 +11551,10 @@
         <v>158</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>79</v>
@@ -11570,7 +11572,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11591,10 +11593,10 @@
         <v>79</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -11605,10 +11607,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11723,10 +11725,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11843,10 +11845,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11872,16 +11874,16 @@
         <v>154</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -11930,7 +11932,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11951,10 +11953,10 @@
         <v>79</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>79</v>
@@ -11965,10 +11967,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12083,10 +12085,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12203,10 +12205,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12232,16 +12234,16 @@
         <v>138</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>79</v>
@@ -12251,7 +12253,7 @@
         <v>79</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>79</v>
@@ -12290,7 +12292,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12311,10 +12313,10 @@
         <v>79</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>79</v>
@@ -12325,10 +12327,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12354,13 +12356,13 @@
         <v>105</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12410,7 +12412,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12431,10 +12433,10 @@
         <v>79</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>79</v>
@@ -12445,10 +12447,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12474,14 +12476,14 @@
         <v>176</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>79</v>
@@ -12530,7 +12532,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12551,10 +12553,10 @@
         <v>79</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>79</v>
@@ -12565,10 +12567,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12594,14 +12596,14 @@
         <v>105</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>79</v>
@@ -12650,7 +12652,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12671,10 +12673,10 @@
         <v>79</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>79</v>
@@ -12685,10 +12687,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12711,19 +12713,19 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>79</v>
@@ -12772,7 +12774,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12793,10 +12795,10 @@
         <v>79</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>79</v>
@@ -12807,10 +12809,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12836,16 +12838,16 @@
         <v>105</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>79</v>
@@ -12894,7 +12896,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12915,10 +12917,10 @@
         <v>79</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>79</v>
@@ -12929,10 +12931,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12958,16 +12960,16 @@
         <v>138</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>79</v>
@@ -12977,10 +12979,10 @@
         <v>79</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>79</v>
@@ -13016,7 +13018,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -13037,13 +13039,13 @@
         <v>79</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>79</v>
@@ -13051,10 +13053,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13080,13 +13082,13 @@
         <v>105</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -13100,7 +13102,7 @@
         <v>79</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>79</v>
@@ -13136,7 +13138,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -13157,13 +13159,13 @@
         <v>79</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>79</v>
@@ -13171,10 +13173,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13197,13 +13199,13 @@
         <v>92</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13254,7 +13256,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13275,13 +13277,13 @@
         <v>79</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>79</v>
@@ -13289,10 +13291,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13315,16 +13317,16 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13374,7 +13376,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13395,13 +13397,13 @@
         <v>79</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>79</v>
@@ -13409,13 +13411,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>79</v>
@@ -13437,17 +13439,17 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>79</v>
@@ -13496,7 +13498,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13505,7 +13507,7 @@
         <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>103</v>
@@ -13517,24 +13519,24 @@
         <v>79</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13649,10 +13651,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13769,10 +13771,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13798,16 +13800,16 @@
         <v>176</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -13832,13 +13834,13 @@
         <v>79</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>79</v>
@@ -13856,7 +13858,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13880,7 +13882,7 @@
         <v>199</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>79</v>
@@ -13891,10 +13893,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13917,19 +13919,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -13939,7 +13941,7 @@
         <v>79</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>79</v>
@@ -13957,10 +13959,10 @@
         <v>158</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>79</v>
@@ -13978,7 +13980,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13999,10 +14001,10 @@
         <v>79</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>79</v>
@@ -14013,10 +14015,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14042,16 +14044,16 @@
         <v>138</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>79</v>
@@ -14061,10 +14063,10 @@
         <v>79</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>79</v>
@@ -14100,7 +14102,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -14121,13 +14123,13 @@
         <v>79</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>79</v>
@@ -14135,10 +14137,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14164,13 +14166,13 @@
         <v>105</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14184,7 +14186,7 @@
         <v>79</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>79</v>
@@ -14220,7 +14222,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14241,13 +14243,13 @@
         <v>79</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>79</v>
@@ -14255,10 +14257,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14281,13 +14283,13 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14338,7 +14340,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14359,13 +14361,13 @@
         <v>79</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>79</v>
@@ -14373,10 +14375,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14399,16 +14401,16 @@
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14458,7 +14460,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14479,13 +14481,13 @@
         <v>79</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>79</v>
@@ -14493,13 +14495,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>79</v>
@@ -14521,17 +14523,17 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>79</v>
@@ -14580,7 +14582,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14589,7 +14591,7 @@
         <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>103</v>
@@ -14601,24 +14603,24 @@
         <v>79</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14733,10 +14735,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14853,10 +14855,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14882,16 +14884,16 @@
         <v>176</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>79</v>
@@ -14916,13 +14918,13 @@
         <v>79</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>79</v>
@@ -14940,7 +14942,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14964,7 +14966,7 @@
         <v>199</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>79</v>
@@ -14975,10 +14977,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15001,19 +15003,19 @@
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>79</v>
@@ -15023,7 +15025,7 @@
         <v>79</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>79</v>
@@ -15041,10 +15043,10 @@
         <v>158</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>79</v>
@@ -15062,7 +15064,7 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -15083,10 +15085,10 @@
         <v>79</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>79</v>
@@ -15097,10 +15099,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15126,16 +15128,16 @@
         <v>138</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>79</v>
@@ -15145,10 +15147,10 @@
         <v>79</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="T102" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U102" t="s" s="2">
         <v>79</v>
@@ -15184,7 +15186,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -15205,13 +15207,13 @@
         <v>79</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>79</v>
@@ -15219,10 +15221,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15248,13 +15250,13 @@
         <v>105</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -15268,7 +15270,7 @@
         <v>79</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>79</v>
@@ -15304,7 +15306,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15325,13 +15327,13 @@
         <v>79</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>79</v>
@@ -15339,10 +15341,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15365,13 +15367,13 @@
         <v>92</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15422,7 +15424,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15443,13 +15445,13 @@
         <v>79</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>79</v>
@@ -15457,10 +15459,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15483,16 +15485,16 @@
         <v>92</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15542,7 +15544,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15563,13 +15565,13 @@
         <v>79</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>79</v>
@@ -15577,10 +15579,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15603,70 +15605,70 @@
         <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q106" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="R106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF106" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="P106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q106" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="R106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15684,27 +15686,27 @@
         <v>79</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15727,19 +15729,19 @@
         <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>79</v>
@@ -15767,16 +15769,16 @@
         <v>166</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
@@ -15786,7 +15788,7 @@
         <v>118</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15807,27 +15809,27 @@
         <v>79</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>79</v>
@@ -15849,19 +15851,19 @@
         <v>92</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>79</v>
@@ -15886,11 +15888,11 @@
         <v>79</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>79</v>
@@ -15908,7 +15910,7 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15929,24 +15931,24 @@
         <v>79</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16061,10 +16063,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16179,13 +16181,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="B111" t="s" s="2">
-        <v>546</v>
-      </c>
       <c r="C111" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>79</v>
@@ -16207,13 +16209,13 @@
         <v>79</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16299,10 +16301,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16417,10 +16419,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16509,7 +16511,7 @@
         <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>120</v>
@@ -16535,10 +16537,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16564,13 +16566,13 @@
         <v>138</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16578,7 +16580,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>79</v>
@@ -16620,7 +16622,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>91</v>
@@ -16655,10 +16657,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16684,10 +16686,10 @@
         <v>176</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>561</v>
+        <v>233</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16699,7 +16701,7 @@
         <v>79</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>79</v>
@@ -16714,7 +16716,7 @@
         <v>79</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
@@ -16736,7 +16738,7 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16745,7 +16747,7 @@
         <v>91</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>103</v>
@@ -16800,16 +16802,16 @@
         <v>154</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>79</v>
@@ -16858,7 +16860,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16879,10 +16881,10 @@
         <v>79</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>79</v>
@@ -17160,16 +17162,16 @@
         <v>138</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -17218,7 +17220,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -17239,10 +17241,10 @@
         <v>79</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>79</v>
@@ -17282,13 +17284,13 @@
         <v>105</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17338,7 +17340,7 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17359,10 +17361,10 @@
         <v>79</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>79</v>
@@ -17405,11 +17407,11 @@
         <v>575</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>79</v>
@@ -17458,7 +17460,7 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17479,10 +17481,10 @@
         <v>79</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>79</v>
@@ -17522,14 +17524,14 @@
         <v>105</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>79</v>
@@ -17578,7 +17580,7 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17599,10 +17601,10 @@
         <v>79</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>79</v>
@@ -17639,19 +17641,19 @@
         <v>92</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>79</v>
@@ -17700,7 +17702,7 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17721,10 +17723,10 @@
         <v>79</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>79</v>
@@ -17764,16 +17766,16 @@
         <v>105</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>79</v>
@@ -17822,7 +17824,7 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17843,10 +17845,10 @@
         <v>79</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>79</v>
@@ -17860,7 +17862,7 @@
         <v>582</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C125" t="s" s="2">
         <v>583</v>
@@ -17885,19 +17887,19 @@
         <v>92</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L125" t="s" s="2">
         <v>584</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>79</v>
@@ -17922,7 +17924,7 @@
         <v>79</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
@@ -17944,7 +17946,7 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17965,16 +17967,16 @@
         <v>79</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="126" hidden="true">
@@ -17982,7 +17984,7 @@
         <v>586</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18100,7 +18102,7 @@
         <v>587</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18246,16 +18248,16 @@
         <v>154</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>79</v>
@@ -18304,7 +18306,7 @@
         <v>79</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18325,10 +18327,10 @@
         <v>79</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>79</v>
@@ -18606,16 +18608,16 @@
         <v>138</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>79</v>
@@ -18664,7 +18666,7 @@
         <v>79</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18685,10 +18687,10 @@
         <v>79</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>79</v>
@@ -18728,13 +18730,13 @@
         <v>105</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18784,7 +18786,7 @@
         <v>79</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18805,10 +18807,10 @@
         <v>79</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>79</v>
@@ -18851,11 +18853,11 @@
         <v>575</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>79</v>
@@ -18904,7 +18906,7 @@
         <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18925,10 +18927,10 @@
         <v>79</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>79</v>
@@ -18968,14 +18970,14 @@
         <v>105</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>79</v>
@@ -19024,7 +19026,7 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -19045,10 +19047,10 @@
         <v>79</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>79</v>
@@ -19085,19 +19087,19 @@
         <v>92</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>79</v>
@@ -19146,7 +19148,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -19167,10 +19169,10 @@
         <v>79</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>79</v>
@@ -19210,16 +19212,16 @@
         <v>105</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>79</v>
@@ -19268,7 +19270,7 @@
         <v>79</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -19289,10 +19291,10 @@
         <v>79</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>79</v>
@@ -19306,7 +19308,7 @@
         <v>597</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C137" t="s" s="2">
         <v>598</v>
@@ -19331,19 +19333,19 @@
         <v>92</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L137" t="s" s="2">
         <v>599</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>79</v>
@@ -19368,7 +19370,7 @@
         <v>79</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
@@ -19390,7 +19392,7 @@
         <v>79</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19411,16 +19413,16 @@
         <v>79</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="138" hidden="true">
@@ -19428,7 +19430,7 @@
         <v>601</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19546,7 +19548,7 @@
         <v>602</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19692,16 +19694,16 @@
         <v>154</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>79</v>
@@ -19750,7 +19752,7 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19771,10 +19773,10 @@
         <v>79</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>79</v>
@@ -20052,16 +20054,16 @@
         <v>138</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>79</v>
@@ -20110,7 +20112,7 @@
         <v>79</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -20131,10 +20133,10 @@
         <v>79</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>79</v>
@@ -20174,13 +20176,13 @@
         <v>105</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -20230,7 +20232,7 @@
         <v>79</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -20251,10 +20253,10 @@
         <v>79</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>79</v>
@@ -20297,11 +20299,11 @@
         <v>575</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>79</v>
@@ -20350,7 +20352,7 @@
         <v>79</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20371,10 +20373,10 @@
         <v>79</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>79</v>
@@ -20414,14 +20416,14 @@
         <v>105</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>79</v>
@@ -20470,7 +20472,7 @@
         <v>79</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20491,10 +20493,10 @@
         <v>79</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>79</v>
@@ -20531,19 +20533,19 @@
         <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>79</v>
@@ -20592,7 +20594,7 @@
         <v>79</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20613,10 +20615,10 @@
         <v>79</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>79</v>
@@ -20656,16 +20658,16 @@
         <v>105</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>79</v>
@@ -20714,7 +20716,7 @@
         <v>79</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20735,10 +20737,10 @@
         <v>79</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>79</v>
@@ -20752,7 +20754,7 @@
         <v>612</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C149" t="s" s="2">
         <v>613</v>
@@ -20777,19 +20779,19 @@
         <v>92</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L149" t="s" s="2">
         <v>614</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>79</v>
@@ -20814,7 +20816,7 @@
         <v>79</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
@@ -20836,7 +20838,7 @@
         <v>79</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20857,16 +20859,16 @@
         <v>617</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="150" hidden="true">
@@ -20874,7 +20876,7 @@
         <v>618</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20992,7 +20994,7 @@
         <v>619</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21081,7 +21083,7 @@
         <v>81</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>120</v>
@@ -21110,10 +21112,10 @@
         <v>620</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>79</v>
@@ -21135,13 +21137,13 @@
         <v>79</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21201,7 +21203,7 @@
         <v>81</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>120</v>
@@ -21230,7 +21232,7 @@
         <v>621</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21348,7 +21350,7 @@
         <v>622</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21437,7 +21439,7 @@
         <v>81</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>120</v>
@@ -21466,7 +21468,7 @@
         <v>623</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21492,13 +21494,13 @@
         <v>138</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21506,7 +21508,7 @@
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>79</v>
@@ -21548,7 +21550,7 @@
         <v>79</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>91</v>
@@ -21586,7 +21588,7 @@
         <v>624</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21612,10 +21614,10 @@
         <v>176</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>561</v>
+        <v>233</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21642,7 +21644,7 @@
         <v>79</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
@@ -21664,7 +21666,7 @@
         <v>79</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21673,7 +21675,7 @@
         <v>91</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ156" t="s" s="2">
         <v>103</v>
@@ -21728,16 +21730,16 @@
         <v>154</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>79</v>
@@ -21786,7 +21788,7 @@
         <v>79</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21795,7 +21797,7 @@
         <v>81</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>103</v>
@@ -21807,10 +21809,10 @@
         <v>79</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>79</v>
@@ -21850,16 +21852,16 @@
         <v>105</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>79</v>
@@ -21908,7 +21910,7 @@
         <v>79</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21917,7 +21919,7 @@
         <v>91</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>103</v>
@@ -21929,10 +21931,10 @@
         <v>79</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>79</v>
@@ -21946,7 +21948,7 @@
         <v>627</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C159" t="s" s="2">
         <v>628</v>
@@ -21971,19 +21973,19 @@
         <v>92</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L159" t="s" s="2">
         <v>629</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>79</v>
@@ -22008,7 +22010,7 @@
         <v>79</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y159" s="2"/>
       <c r="Z159" t="s" s="2">
@@ -22030,7 +22032,7 @@
         <v>79</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -22051,16 +22053,16 @@
         <v>79</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="160" hidden="true">
@@ -22068,7 +22070,7 @@
         <v>632</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22186,7 +22188,7 @@
         <v>633</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22275,7 +22277,7 @@
         <v>81</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>120</v>
@@ -22304,10 +22306,10 @@
         <v>634</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D162" t="s" s="2">
         <v>79</v>
@@ -22329,13 +22331,13 @@
         <v>79</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -22395,7 +22397,7 @@
         <v>81</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>120</v>
@@ -22424,7 +22426,7 @@
         <v>635</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22542,7 +22544,7 @@
         <v>636</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22631,7 +22633,7 @@
         <v>81</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>120</v>
@@ -22660,7 +22662,7 @@
         <v>637</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22686,13 +22688,13 @@
         <v>138</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -22700,7 +22702,7 @@
       </c>
       <c r="Q165" s="2"/>
       <c r="R165" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>79</v>
@@ -22742,7 +22744,7 @@
         <v>79</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>91</v>
@@ -22780,7 +22782,7 @@
         <v>638</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22806,10 +22808,10 @@
         <v>176</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>561</v>
+        <v>233</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -22836,7 +22838,7 @@
         <v>79</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y166" s="2"/>
       <c r="Z166" t="s" s="2">
@@ -22858,7 +22860,7 @@
         <v>79</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22867,7 +22869,7 @@
         <v>91</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>103</v>
@@ -22922,16 +22924,16 @@
         <v>154</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>79</v>
@@ -22980,7 +22982,7 @@
         <v>79</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22989,7 +22991,7 @@
         <v>81</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ167" t="s" s="2">
         <v>103</v>
@@ -23001,10 +23003,10 @@
         <v>79</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>79</v>
@@ -23044,16 +23046,16 @@
         <v>105</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>79</v>
@@ -23102,7 +23104,7 @@
         <v>79</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -23111,7 +23113,7 @@
         <v>91</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>103</v>
@@ -23123,10 +23125,10 @@
         <v>79</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>79</v>
@@ -23140,7 +23142,7 @@
         <v>641</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C169" t="s" s="2">
         <v>642</v>
@@ -23165,19 +23167,19 @@
         <v>92</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L169" t="s" s="2">
         <v>643</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>79</v>
@@ -23202,7 +23204,7 @@
         <v>79</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y169" s="2"/>
       <c r="Z169" t="s" s="2">
@@ -23224,7 +23226,7 @@
         <v>79</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -23245,16 +23247,16 @@
         <v>617</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="170" hidden="true">
@@ -23262,7 +23264,7 @@
         <v>645</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23380,7 +23382,7 @@
         <v>646</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23469,7 +23471,7 @@
         <v>81</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>120</v>
@@ -23498,10 +23500,10 @@
         <v>647</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D172" t="s" s="2">
         <v>79</v>
@@ -23523,13 +23525,13 @@
         <v>79</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -23589,7 +23591,7 @@
         <v>81</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>120</v>
@@ -23618,7 +23620,7 @@
         <v>648</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23736,7 +23738,7 @@
         <v>649</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23825,7 +23827,7 @@
         <v>81</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ174" t="s" s="2">
         <v>120</v>
@@ -23854,7 +23856,7 @@
         <v>650</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23880,13 +23882,13 @@
         <v>138</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -23894,7 +23896,7 @@
       </c>
       <c r="Q175" s="2"/>
       <c r="R175" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S175" t="s" s="2">
         <v>79</v>
@@ -23936,7 +23938,7 @@
         <v>79</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>91</v>
@@ -23974,7 +23976,7 @@
         <v>651</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24000,10 +24002,10 @@
         <v>176</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>561</v>
+        <v>233</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -24030,7 +24032,7 @@
         <v>79</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
@@ -24052,7 +24054,7 @@
         <v>79</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -24061,7 +24063,7 @@
         <v>91</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>103</v>
@@ -24116,16 +24118,16 @@
         <v>154</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>79</v>
@@ -24174,7 +24176,7 @@
         <v>79</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -24183,7 +24185,7 @@
         <v>81</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ177" t="s" s="2">
         <v>103</v>
@@ -24195,10 +24197,10 @@
         <v>79</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>79</v>
@@ -24238,16 +24240,16 @@
         <v>105</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>79</v>
@@ -24296,7 +24298,7 @@
         <v>79</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -24305,7 +24307,7 @@
         <v>91</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ178" t="s" s="2">
         <v>103</v>
@@ -24317,10 +24319,10 @@
         <v>79</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>79</v>
@@ -24334,7 +24336,7 @@
         <v>654</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C179" t="s" s="2">
         <v>655</v>
@@ -24359,19 +24361,19 @@
         <v>92</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L179" t="s" s="2">
         <v>656</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>79</v>
@@ -24399,10 +24401,10 @@
         <v>166</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>79</v>
@@ -24420,7 +24422,7 @@
         <v>79</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -24441,16 +24443,16 @@
         <v>79</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP179" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="180" hidden="true">
@@ -24458,7 +24460,7 @@
         <v>657</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24576,7 +24578,7 @@
         <v>658</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24665,7 +24667,7 @@
         <v>81</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>120</v>
@@ -24694,10 +24696,10 @@
         <v>659</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>79</v>
@@ -24719,13 +24721,13 @@
         <v>79</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -24785,7 +24787,7 @@
         <v>81</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>120</v>
@@ -24814,7 +24816,7 @@
         <v>660</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24932,7 +24934,7 @@
         <v>661</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25021,7 +25023,7 @@
         <v>81</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>120</v>
@@ -25050,7 +25052,7 @@
         <v>662</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25076,13 +25078,13 @@
         <v>138</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -25090,7 +25092,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>79</v>
@@ -25132,7 +25134,7 @@
         <v>79</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>91</v>
@@ -25170,7 +25172,7 @@
         <v>663</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25196,10 +25198,10 @@
         <v>176</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>561</v>
+        <v>233</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -25226,7 +25228,7 @@
         <v>79</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y186" s="2"/>
       <c r="Z186" t="s" s="2">
@@ -25248,7 +25250,7 @@
         <v>79</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -25257,7 +25259,7 @@
         <v>91</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>103</v>
@@ -25312,16 +25314,16 @@
         <v>154</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>79</v>
@@ -25370,7 +25372,7 @@
         <v>79</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -25379,7 +25381,7 @@
         <v>81</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>103</v>
@@ -25391,10 +25393,10 @@
         <v>79</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>79</v>
@@ -25434,16 +25436,16 @@
         <v>105</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>79</v>
@@ -25492,7 +25494,7 @@
         <v>79</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -25501,7 +25503,7 @@
         <v>91</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ188" t="s" s="2">
         <v>103</v>
@@ -25513,10 +25515,10 @@
         <v>79</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>79</v>
@@ -25623,7 +25625,7 @@
         <v>91</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>103</v>
@@ -26308,7 +26310,7 @@
         <v>79</v>
       </c>
       <c r="X195" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y195" t="s" s="2">
         <v>705</v>
@@ -26481,7 +26483,7 @@
         <v>719</v>
       </c>
       <c r="AO196" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP196" t="s" s="2">
         <v>79</v>
@@ -26552,7 +26554,7 @@
         <v>79</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y197" t="s" s="2">
         <v>725</v>
@@ -26757,7 +26759,7 @@
         <v>92</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L199" t="s" s="2">
         <v>738</v>
@@ -26841,7 +26843,7 @@
         <v>741</v>
       </c>
       <c r="AO199" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP199" t="s" s="2">
         <v>79</v>
@@ -27201,7 +27203,7 @@
         <v>79</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN202" t="s" s="2">
         <v>764</v>
@@ -27638,7 +27640,7 @@
       </c>
       <c r="Y206" s="2"/>
       <c r="Z206" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>79</v>
@@ -27717,7 +27719,7 @@
         <v>92</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L207" t="s" s="2">
         <v>779</v>
@@ -28329,7 +28331,7 @@
         <v>115</v>
       </c>
       <c r="O212" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P212" t="s" s="2">
         <v>79</v>
@@ -28439,7 +28441,7 @@
         <v>79</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L213" t="s" s="2">
         <v>804</v>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8295" uniqueCount="830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8294" uniqueCount="830">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T12:18:24+00:00</t>
+    <t>2024-04-10T12:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -692,9 +692,6 @@
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
     <t>The date range that this organization should be considered available.</t>
   </si>
   <si>
@@ -744,7 +741,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -784,8 +781,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t>ele-1
-per-1</t>
+    <t xml:space="preserve">per-1
+</t>
   </si>
   <si>
     <t>dateCreation</t>
@@ -1761,6 +1758,9 @@
   </si>
   <si>
     <t>Organization.type.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-organization-types</t>
@@ -5504,10 +5504,10 @@
         <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5582,7 +5582,7 @@
         <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>79</v>
@@ -5593,10 +5593,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5711,14 +5711,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5740,14 +5740,12 @@
         <v>112</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>113</v>
+        <v>201</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -5805,7 +5803,7 @@
         <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>120</v>
@@ -5820,7 +5818,7 @@
         <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -5831,10 +5829,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5860,13 +5858,13 @@
         <v>138</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5874,49 +5872,49 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="S25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>91</v>
@@ -5951,10 +5949,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5977,13 +5975,13 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -6034,7 +6032,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -6043,7 +6041,7 @@
         <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>103</v>
@@ -6069,10 +6067,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6187,10 +6185,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6281,7 +6279,7 @@
         <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>120</v>
@@ -6296,7 +6294,7 @@
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>199</v>
+        <v>109</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -6307,10 +6305,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6333,16 +6331,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6392,31 +6390,31 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI29" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -6427,10 +6425,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6453,69 +6451,69 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q30" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="R30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="R30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>257</v>
-      </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
@@ -6523,22 +6521,22 @@
         <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -6549,13 +6547,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>79</v>
@@ -6577,13 +6575,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6669,13 +6667,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>79</v>
@@ -6697,13 +6695,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6769,7 +6767,7 @@
         <v>120</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>79</v>
@@ -6789,13 +6787,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>79</v>
@@ -6817,13 +6815,13 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6892,7 +6890,7 @@
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
@@ -6909,13 +6907,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>79</v>
@@ -6937,13 +6935,13 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -7009,10 +7007,10 @@
         <v>120</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
@@ -7029,13 +7027,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>79</v>
@@ -7057,13 +7055,13 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -7132,7 +7130,7 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
@@ -7149,13 +7147,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>79</v>
@@ -7177,13 +7175,13 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -7269,10 +7267,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7298,16 +7296,16 @@
         <v>112</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -7356,7 +7354,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -7391,10 +7389,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7417,17 +7415,17 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -7464,10 +7462,10 @@
         <v>79</v>
       </c>
       <c r="AB38" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AC38" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>79</v>
@@ -7476,7 +7474,7 @@
         <v>118</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7485,7 +7483,7 @@
         <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>103</v>
@@ -7497,27 +7495,27 @@
         <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AO38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>311</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C39" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>79</v>
@@ -7539,17 +7537,17 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -7598,7 +7596,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7607,36 +7605,36 @@
         <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AO39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>311</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7751,10 +7749,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B41" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7871,10 +7869,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B42" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7900,16 +7898,16 @@
         <v>176</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -7919,46 +7917,46 @@
         <v>79</v>
       </c>
       <c r="S42" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X42" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="T42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X42" t="s" s="2">
+      <c r="Y42" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="Y42" t="s" s="2">
+      <c r="Z42" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="Z42" t="s" s="2">
+      <c r="AA42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7982,7 +7980,7 @@
         <v>199</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -7993,10 +7991,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8019,19 +8017,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -8041,7 +8039,7 @@
         <v>79</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>79</v>
@@ -8059,28 +8057,28 @@
         <v>158</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="Z43" t="s" s="2">
+      <c r="AA43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -8101,10 +8099,10 @@
         <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -8115,10 +8113,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8144,16 +8142,16 @@
         <v>138</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -8163,46 +8161,46 @@
         <v>79</v>
       </c>
       <c r="S44" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="T44" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="T44" t="s" s="2">
+      <c r="U44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -8223,13 +8221,13 @@
         <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -8237,10 +8235,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8266,13 +8264,13 @@
         <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8286,43 +8284,43 @@
         <v>79</v>
       </c>
       <c r="T45" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -8343,13 +8341,13 @@
         <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>79</v>
@@ -8357,10 +8355,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8383,13 +8381,13 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8440,7 +8438,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8461,13 +8459,13 @@
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>79</v>
@@ -8475,10 +8473,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8501,16 +8499,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8560,7 +8558,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8581,13 +8579,13 @@
         <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>79</v>
@@ -8595,13 +8593,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C48" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>79</v>
@@ -8623,17 +8621,17 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -8682,7 +8680,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8691,36 +8689,36 @@
         <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>311</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8835,10 +8833,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8955,10 +8953,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8984,16 +8982,16 @@
         <v>176</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -9018,31 +9016,31 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Y51" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="Y51" t="s" s="2">
+      <c r="Z51" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="Z51" t="s" s="2">
+      <c r="AA51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -9066,7 +9064,7 @@
         <v>199</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -9077,10 +9075,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9103,19 +9101,19 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -9143,28 +9141,28 @@
         <v>158</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="Z52" t="s" s="2">
+      <c r="AA52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -9185,10 +9183,10 @@
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -9199,10 +9197,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9317,10 +9315,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9437,10 +9435,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9466,16 +9464,16 @@
         <v>154</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -9524,7 +9522,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9545,10 +9543,10 @@
         <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -9559,10 +9557,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9677,10 +9675,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9797,10 +9795,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9826,16 +9824,16 @@
         <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -9845,46 +9843,46 @@
         <v>79</v>
       </c>
       <c r="S58" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF58" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9905,10 +9903,10 @@
         <v>79</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -9919,10 +9917,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9948,13 +9946,13 @@
         <v>105</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10004,7 +10002,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -10025,10 +10023,10 @@
         <v>79</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -10039,10 +10037,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10068,14 +10066,14 @@
         <v>176</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -10124,7 +10122,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -10145,10 +10143,10 @@
         <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -10159,10 +10157,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10188,14 +10186,14 @@
         <v>105</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -10244,7 +10242,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -10265,10 +10263,10 @@
         <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -10279,10 +10277,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10305,19 +10303,19 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
@@ -10366,7 +10364,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10387,10 +10385,10 @@
         <v>79</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -10401,10 +10399,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10430,16 +10428,16 @@
         <v>105</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -10488,7 +10486,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10509,10 +10507,10 @@
         <v>79</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -10523,10 +10521,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10552,16 +10550,16 @@
         <v>138</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -10571,46 +10569,46 @@
         <v>79</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="T64" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10631,13 +10629,13 @@
         <v>79</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>79</v>
@@ -10645,10 +10643,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10674,13 +10672,13 @@
         <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="M65" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10694,43 +10692,43 @@
         <v>79</v>
       </c>
       <c r="T65" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10751,13 +10749,13 @@
         <v>79</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>79</v>
@@ -10765,10 +10763,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10791,13 +10789,13 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10848,7 +10846,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10869,13 +10867,13 @@
         <v>79</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>79</v>
@@ -10883,10 +10881,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10909,16 +10907,16 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10968,7 +10966,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10989,13 +10987,13 @@
         <v>79</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>79</v>
@@ -11003,13 +11001,13 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C68" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>79</v>
@@ -11031,17 +11029,17 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -11090,7 +11088,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -11099,36 +11097,36 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AO68" t="s" s="2">
+      <c r="AP68" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>311</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11243,10 +11241,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11363,10 +11361,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11392,16 +11390,16 @@
         <v>176</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -11426,31 +11424,31 @@
         <v>79</v>
       </c>
       <c r="X71" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Y71" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="Y71" t="s" s="2">
+      <c r="Z71" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="Z71" t="s" s="2">
+      <c r="AA71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11474,7 +11472,7 @@
         <v>199</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -11485,10 +11483,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11511,19 +11509,19 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
@@ -11551,28 +11549,28 @@
         <v>158</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="Z72" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="Z72" t="s" s="2">
+      <c r="AA72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11593,10 +11591,10 @@
         <v>79</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -11607,10 +11605,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11725,10 +11723,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11845,10 +11843,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11874,16 +11872,16 @@
         <v>154</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -11932,7 +11930,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11953,10 +11951,10 @@
         <v>79</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>79</v>
@@ -11967,10 +11965,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12085,10 +12083,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12205,10 +12203,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12234,16 +12232,16 @@
         <v>138</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>79</v>
@@ -12253,46 +12251,46 @@
         <v>79</v>
       </c>
       <c r="S78" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12313,10 +12311,10 @@
         <v>79</v>
       </c>
       <c r="AM78" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>79</v>
@@ -12327,10 +12325,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12356,13 +12354,13 @@
         <v>105</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12412,7 +12410,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12433,10 +12431,10 @@
         <v>79</v>
       </c>
       <c r="AM79" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>79</v>
@@ -12447,10 +12445,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12476,14 +12474,14 @@
         <v>176</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>79</v>
@@ -12532,7 +12530,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12553,10 +12551,10 @@
         <v>79</v>
       </c>
       <c r="AM80" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>79</v>
@@ -12567,10 +12565,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12596,14 +12594,14 @@
         <v>105</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>79</v>
@@ -12652,7 +12650,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12673,10 +12671,10 @@
         <v>79</v>
       </c>
       <c r="AM81" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>79</v>
@@ -12687,10 +12685,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12713,19 +12711,19 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>79</v>
@@ -12774,7 +12772,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12795,10 +12793,10 @@
         <v>79</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>79</v>
@@ -12809,10 +12807,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12838,16 +12836,16 @@
         <v>105</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>79</v>
@@ -12896,7 +12894,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12917,10 +12915,10 @@
         <v>79</v>
       </c>
       <c r="AM83" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>79</v>
@@ -12931,10 +12929,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12960,16 +12958,16 @@
         <v>138</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>79</v>
@@ -12979,46 +12977,46 @@
         <v>79</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="T84" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -13039,13 +13037,13 @@
         <v>79</v>
       </c>
       <c r="AM84" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AN84" t="s" s="2">
+      <c r="AO84" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>79</v>
@@ -13053,10 +13051,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13082,13 +13080,13 @@
         <v>105</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="M85" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -13102,43 +13100,43 @@
         <v>79</v>
       </c>
       <c r="T85" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -13159,13 +13157,13 @@
         <v>79</v>
       </c>
       <c r="AM85" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AN85" t="s" s="2">
+      <c r="AO85" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>79</v>
@@ -13173,10 +13171,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13199,13 +13197,13 @@
         <v>92</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13256,7 +13254,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13277,13 +13275,13 @@
         <v>79</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="AN86" t="s" s="2">
+      <c r="AO86" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>79</v>
@@ -13291,10 +13289,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13317,16 +13315,16 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13376,7 +13374,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13397,13 +13395,13 @@
         <v>79</v>
       </c>
       <c r="AM87" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AN87" t="s" s="2">
+      <c r="AO87" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>79</v>
@@ -13411,13 +13409,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C88" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>79</v>
@@ -13439,17 +13437,17 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>79</v>
@@ -13498,7 +13496,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13507,7 +13505,7 @@
         <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>103</v>
@@ -13519,24 +13517,24 @@
         <v>79</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AN88" t="s" s="2">
+      <c r="AO88" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AO88" t="s" s="2">
+      <c r="AP88" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>311</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13651,10 +13649,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13771,10 +13769,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13800,16 +13798,16 @@
         <v>176</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -13834,31 +13832,31 @@
         <v>79</v>
       </c>
       <c r="X91" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Y91" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="Y91" t="s" s="2">
+      <c r="Z91" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="Z91" t="s" s="2">
+      <c r="AA91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13882,7 +13880,7 @@
         <v>199</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>79</v>
@@ -13893,10 +13891,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13919,19 +13917,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -13941,7 +13939,7 @@
         <v>79</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>79</v>
@@ -13959,28 +13957,28 @@
         <v>158</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="Z92" t="s" s="2">
+      <c r="AA92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -14001,10 +13999,10 @@
         <v>79</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>79</v>
@@ -14015,10 +14013,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14044,16 +14042,16 @@
         <v>138</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="N93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>79</v>
@@ -14063,46 +14061,46 @@
         <v>79</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="T93" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -14123,13 +14121,13 @@
         <v>79</v>
       </c>
       <c r="AM93" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>79</v>
@@ -14137,10 +14135,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14166,13 +14164,13 @@
         <v>105</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="M94" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14186,43 +14184,43 @@
         <v>79</v>
       </c>
       <c r="T94" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14243,13 +14241,13 @@
         <v>79</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AN94" t="s" s="2">
+      <c r="AO94" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>79</v>
@@ -14257,10 +14255,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14283,13 +14281,13 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14340,7 +14338,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14361,13 +14359,13 @@
         <v>79</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="AN95" t="s" s="2">
+      <c r="AO95" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>79</v>
@@ -14375,10 +14373,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14401,16 +14399,16 @@
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14460,7 +14458,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14481,13 +14479,13 @@
         <v>79</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AN96" t="s" s="2">
+      <c r="AO96" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>79</v>
@@ -14495,13 +14493,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C97" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>79</v>
@@ -14523,17 +14521,17 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>79</v>
@@ -14582,7 +14580,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14591,7 +14589,7 @@
         <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>103</v>
@@ -14603,24 +14601,24 @@
         <v>79</v>
       </c>
       <c r="AM97" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AN97" t="s" s="2">
+      <c r="AO97" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AO97" t="s" s="2">
+      <c r="AP97" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>311</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14735,10 +14733,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14855,10 +14853,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14884,16 +14882,16 @@
         <v>176</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>79</v>
@@ -14918,31 +14916,31 @@
         <v>79</v>
       </c>
       <c r="X100" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Y100" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="Y100" t="s" s="2">
+      <c r="Z100" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="Z100" t="s" s="2">
+      <c r="AA100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14966,7 +14964,7 @@
         <v>199</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>79</v>
@@ -14977,10 +14975,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15003,19 +15001,19 @@
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>79</v>
@@ -15025,7 +15023,7 @@
         <v>79</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>79</v>
@@ -15043,28 +15041,28 @@
         <v>158</v>
       </c>
       <c r="Y101" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="Z101" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="Z101" t="s" s="2">
+      <c r="AA101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -15085,10 +15083,10 @@
         <v>79</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>79</v>
@@ -15099,10 +15097,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15128,16 +15126,16 @@
         <v>138</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="N102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>79</v>
@@ -15147,46 +15145,46 @@
         <v>79</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T102" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF102" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -15207,13 +15205,13 @@
         <v>79</v>
       </c>
       <c r="AM102" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AN102" t="s" s="2">
+      <c r="AO102" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>79</v>
@@ -15221,10 +15219,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15250,13 +15248,13 @@
         <v>105</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="M103" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -15270,43 +15268,43 @@
         <v>79</v>
       </c>
       <c r="T103" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF103" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15327,13 +15325,13 @@
         <v>79</v>
       </c>
       <c r="AM103" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AN103" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AN103" t="s" s="2">
+      <c r="AO103" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>79</v>
@@ -15341,10 +15339,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15367,13 +15365,13 @@
         <v>92</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15424,7 +15422,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15445,13 +15443,13 @@
         <v>79</v>
       </c>
       <c r="AM104" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="AN104" t="s" s="2">
+      <c r="AO104" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>79</v>
@@ -15459,10 +15457,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15485,16 +15483,16 @@
         <v>92</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L105" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="M105" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15544,7 +15542,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15565,13 +15563,13 @@
         <v>79</v>
       </c>
       <c r="AM105" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AN105" t="s" s="2">
+      <c r="AO105" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>79</v>
@@ -15579,10 +15577,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15605,26 +15603,26 @@
         <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="N106" t="s" s="2">
+      <c r="O106" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="O106" t="s" s="2">
+      <c r="P106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q106" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="P106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q106" t="s" s="2">
-        <v>523</v>
-      </c>
       <c r="R106" t="s" s="2">
         <v>79</v>
       </c>
@@ -15668,7 +15666,7 @@
         <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15686,27 +15684,27 @@
         <v>79</v>
       </c>
       <c r="AL106" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AM106" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="AM106" t="s" s="2">
+      <c r="AN106" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="AN106" t="s" s="2">
+      <c r="AO106" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AO106" t="s" s="2">
+      <c r="AP106" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AP106" t="s" s="2">
-        <v>528</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15729,19 +15727,19 @@
         <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>79</v>
@@ -15769,16 +15767,16 @@
         <v>166</v>
       </c>
       <c r="Y107" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="Z107" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="Z107" t="s" s="2">
+      <c r="AA107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB107" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
@@ -15788,7 +15786,7 @@
         <v>118</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15809,27 +15807,27 @@
         <v>79</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="C108" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>79</v>
@@ -15851,19 +15849,19 @@
         <v>92</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="M108" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="N108" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="N108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>79</v>
@@ -15888,11 +15886,11 @@
         <v>79</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>79</v>
@@ -15910,7 +15908,7 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15931,24 +15929,24 @@
         <v>79</v>
       </c>
       <c r="AM108" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B109" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16063,10 +16061,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B110" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16181,13 +16179,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C111" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="C111" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>79</v>
@@ -16209,13 +16207,13 @@
         <v>79</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16301,10 +16299,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B112" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16419,10 +16417,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16511,7 +16509,7 @@
         <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>120</v>
@@ -16537,10 +16535,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B114" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16566,13 +16564,13 @@
         <v>138</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16580,7 +16578,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>79</v>
@@ -16622,7 +16620,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>91</v>
@@ -16657,10 +16655,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B115" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16686,10 +16684,10 @@
         <v>176</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>233</v>
+        <v>561</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16701,7 +16699,7 @@
         <v>79</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>79</v>
@@ -16716,7 +16714,7 @@
         <v>79</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
@@ -16738,7 +16736,7 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16747,7 +16745,7 @@
         <v>91</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>103</v>
@@ -16802,16 +16800,16 @@
         <v>154</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="N116" t="s" s="2">
+      <c r="O116" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>79</v>
@@ -16860,7 +16858,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16881,10 +16879,10 @@
         <v>79</v>
       </c>
       <c r="AM116" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AN116" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>79</v>
@@ -17162,16 +17160,16 @@
         <v>138</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="N119" t="s" s="2">
+      <c r="O119" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -17220,7 +17218,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -17241,10 +17239,10 @@
         <v>79</v>
       </c>
       <c r="AM119" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AN119" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>79</v>
@@ -17284,13 +17282,13 @@
         <v>105</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17340,7 +17338,7 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17361,10 +17359,10 @@
         <v>79</v>
       </c>
       <c r="AM120" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN120" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>79</v>
@@ -17407,11 +17405,11 @@
         <v>575</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>79</v>
@@ -17460,7 +17458,7 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17481,10 +17479,10 @@
         <v>79</v>
       </c>
       <c r="AM121" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AN121" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>79</v>
@@ -17524,14 +17522,14 @@
         <v>105</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>79</v>
@@ -17580,7 +17578,7 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17601,10 +17599,10 @@
         <v>79</v>
       </c>
       <c r="AM122" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>79</v>
@@ -17641,19 +17639,19 @@
         <v>92</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L123" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="M123" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N123" t="s" s="2">
+      <c r="O123" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>79</v>
@@ -17702,7 +17700,7 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17723,10 +17721,10 @@
         <v>79</v>
       </c>
       <c r="AM123" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>79</v>
@@ -17766,16 +17764,16 @@
         <v>105</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N124" t="s" s="2">
+      <c r="O124" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>79</v>
@@ -17824,7 +17822,7 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17845,10 +17843,10 @@
         <v>79</v>
       </c>
       <c r="AM124" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AN124" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>79</v>
@@ -17862,7 +17860,7 @@
         <v>582</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C125" t="s" s="2">
         <v>583</v>
@@ -17887,19 +17885,19 @@
         <v>92</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L125" t="s" s="2">
         <v>584</v>
       </c>
       <c r="M125" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="N125" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="N125" t="s" s="2">
+      <c r="O125" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>79</v>
@@ -17924,7 +17922,7 @@
         <v>79</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
@@ -17946,7 +17944,7 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17967,16 +17965,16 @@
         <v>79</v>
       </c>
       <c r="AM125" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="126" hidden="true">
@@ -17984,7 +17982,7 @@
         <v>586</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18102,7 +18100,7 @@
         <v>587</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18248,16 +18246,16 @@
         <v>154</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>79</v>
@@ -18306,7 +18304,7 @@
         <v>79</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18327,10 +18325,10 @@
         <v>79</v>
       </c>
       <c r="AM128" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AN128" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>79</v>
@@ -18608,16 +18606,16 @@
         <v>138</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="N131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>79</v>
@@ -18666,7 +18664,7 @@
         <v>79</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18687,10 +18685,10 @@
         <v>79</v>
       </c>
       <c r="AM131" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AN131" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>79</v>
@@ -18730,13 +18728,13 @@
         <v>105</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18786,7 +18784,7 @@
         <v>79</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18807,10 +18805,10 @@
         <v>79</v>
       </c>
       <c r="AM132" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN132" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>79</v>
@@ -18853,11 +18851,11 @@
         <v>575</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>79</v>
@@ -18906,7 +18904,7 @@
         <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18927,10 +18925,10 @@
         <v>79</v>
       </c>
       <c r="AM133" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AN133" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>79</v>
@@ -18970,14 +18968,14 @@
         <v>105</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>79</v>
@@ -19026,7 +19024,7 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -19047,10 +19045,10 @@
         <v>79</v>
       </c>
       <c r="AM134" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AN134" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>79</v>
@@ -19087,19 +19085,19 @@
         <v>92</v>
       </c>
       <c r="K135" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L135" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="L135" t="s" s="2">
+      <c r="M135" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N135" t="s" s="2">
+      <c r="O135" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>79</v>
@@ -19148,7 +19146,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -19169,10 +19167,10 @@
         <v>79</v>
       </c>
       <c r="AM135" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AN135" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>79</v>
@@ -19212,16 +19210,16 @@
         <v>105</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N136" t="s" s="2">
+      <c r="O136" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>79</v>
@@ -19270,7 +19268,7 @@
         <v>79</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -19291,10 +19289,10 @@
         <v>79</v>
       </c>
       <c r="AM136" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AN136" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AN136" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>79</v>
@@ -19308,7 +19306,7 @@
         <v>597</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C137" t="s" s="2">
         <v>598</v>
@@ -19333,19 +19331,19 @@
         <v>92</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L137" t="s" s="2">
         <v>599</v>
       </c>
       <c r="M137" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="N137" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="N137" t="s" s="2">
+      <c r="O137" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>79</v>
@@ -19370,7 +19368,7 @@
         <v>79</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
@@ -19392,7 +19390,7 @@
         <v>79</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19413,16 +19411,16 @@
         <v>79</v>
       </c>
       <c r="AM137" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AN137" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="AN137" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="138" hidden="true">
@@ -19430,7 +19428,7 @@
         <v>601</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19548,7 +19546,7 @@
         <v>602</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19694,16 +19692,16 @@
         <v>154</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M140" t="s" s="2">
+      <c r="N140" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="N140" t="s" s="2">
+      <c r="O140" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>79</v>
@@ -19752,7 +19750,7 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19773,10 +19771,10 @@
         <v>79</v>
       </c>
       <c r="AM140" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AN140" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AN140" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>79</v>
@@ -20054,16 +20052,16 @@
         <v>138</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="N143" t="s" s="2">
+      <c r="O143" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>79</v>
@@ -20112,7 +20110,7 @@
         <v>79</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -20133,10 +20131,10 @@
         <v>79</v>
       </c>
       <c r="AM143" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AN143" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AN143" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>79</v>
@@ -20176,13 +20174,13 @@
         <v>105</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M144" t="s" s="2">
+      <c r="N144" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -20232,7 +20230,7 @@
         <v>79</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -20253,10 +20251,10 @@
         <v>79</v>
       </c>
       <c r="AM144" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN144" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AN144" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>79</v>
@@ -20299,11 +20297,11 @@
         <v>575</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>79</v>
@@ -20352,7 +20350,7 @@
         <v>79</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20373,10 +20371,10 @@
         <v>79</v>
       </c>
       <c r="AM145" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AN145" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AN145" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>79</v>
@@ -20416,14 +20414,14 @@
         <v>105</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M146" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>79</v>
@@ -20472,7 +20470,7 @@
         <v>79</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20493,10 +20491,10 @@
         <v>79</v>
       </c>
       <c r="AM146" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AN146" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AN146" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>79</v>
@@ -20533,19 +20531,19 @@
         <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L147" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="L147" t="s" s="2">
+      <c r="M147" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="N147" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N147" t="s" s="2">
+      <c r="O147" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>79</v>
@@ -20594,7 +20592,7 @@
         <v>79</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20615,10 +20613,10 @@
         <v>79</v>
       </c>
       <c r="AM147" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AN147" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AN147" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>79</v>
@@ -20658,16 +20656,16 @@
         <v>105</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="N148" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N148" t="s" s="2">
+      <c r="O148" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>79</v>
@@ -20716,7 +20714,7 @@
         <v>79</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20737,10 +20735,10 @@
         <v>79</v>
       </c>
       <c r="AM148" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AN148" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AN148" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>79</v>
@@ -20754,7 +20752,7 @@
         <v>612</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C149" t="s" s="2">
         <v>613</v>
@@ -20779,19 +20777,19 @@
         <v>92</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L149" t="s" s="2">
         <v>614</v>
       </c>
       <c r="M149" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="N149" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="N149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>79</v>
@@ -20816,7 +20814,7 @@
         <v>79</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
@@ -20838,7 +20836,7 @@
         <v>79</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20859,16 +20857,16 @@
         <v>617</v>
       </c>
       <c r="AM149" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AN149" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="AN149" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="150" hidden="true">
@@ -20876,7 +20874,7 @@
         <v>618</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20994,7 +20992,7 @@
         <v>619</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21083,7 +21081,7 @@
         <v>81</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>120</v>
@@ -21112,10 +21110,10 @@
         <v>620</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>79</v>
@@ -21137,13 +21135,13 @@
         <v>79</v>
       </c>
       <c r="K152" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="L152" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="L152" t="s" s="2">
+      <c r="M152" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21203,7 +21201,7 @@
         <v>81</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>120</v>
@@ -21232,7 +21230,7 @@
         <v>621</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21350,7 +21348,7 @@
         <v>622</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21439,7 +21437,7 @@
         <v>81</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>120</v>
@@ -21468,7 +21466,7 @@
         <v>623</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21494,13 +21492,13 @@
         <v>138</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="M155" t="s" s="2">
+      <c r="N155" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21508,7 +21506,7 @@
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>79</v>
@@ -21550,7 +21548,7 @@
         <v>79</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>91</v>
@@ -21588,7 +21586,7 @@
         <v>624</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21614,10 +21612,10 @@
         <v>176</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>233</v>
+        <v>561</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21644,7 +21642,7 @@
         <v>79</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
@@ -21666,7 +21664,7 @@
         <v>79</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21675,7 +21673,7 @@
         <v>91</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ156" t="s" s="2">
         <v>103</v>
@@ -21730,16 +21728,16 @@
         <v>154</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="N157" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="N157" t="s" s="2">
+      <c r="O157" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>79</v>
@@ -21788,7 +21786,7 @@
         <v>79</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21797,7 +21795,7 @@
         <v>81</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>103</v>
@@ -21809,10 +21807,10 @@
         <v>79</v>
       </c>
       <c r="AM157" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AN157" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AN157" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>79</v>
@@ -21852,16 +21850,16 @@
         <v>105</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M158" t="s" s="2">
+      <c r="N158" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N158" t="s" s="2">
+      <c r="O158" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>79</v>
@@ -21910,7 +21908,7 @@
         <v>79</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21919,7 +21917,7 @@
         <v>91</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>103</v>
@@ -21931,10 +21929,10 @@
         <v>79</v>
       </c>
       <c r="AM158" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AN158" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AN158" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>79</v>
@@ -21948,7 +21946,7 @@
         <v>627</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C159" t="s" s="2">
         <v>628</v>
@@ -21973,19 +21971,19 @@
         <v>92</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L159" t="s" s="2">
         <v>629</v>
       </c>
       <c r="M159" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="N159" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="N159" t="s" s="2">
+      <c r="O159" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>79</v>
@@ -22010,7 +22008,7 @@
         <v>79</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y159" s="2"/>
       <c r="Z159" t="s" s="2">
@@ -22032,7 +22030,7 @@
         <v>79</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -22053,16 +22051,16 @@
         <v>79</v>
       </c>
       <c r="AM159" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AN159" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="AN159" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="160" hidden="true">
@@ -22070,7 +22068,7 @@
         <v>632</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22188,7 +22186,7 @@
         <v>633</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22277,7 +22275,7 @@
         <v>81</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>120</v>
@@ -22306,10 +22304,10 @@
         <v>634</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D162" t="s" s="2">
         <v>79</v>
@@ -22331,13 +22329,13 @@
         <v>79</v>
       </c>
       <c r="K162" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="L162" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="L162" t="s" s="2">
+      <c r="M162" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -22397,7 +22395,7 @@
         <v>81</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>120</v>
@@ -22426,7 +22424,7 @@
         <v>635</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22544,7 +22542,7 @@
         <v>636</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22633,7 +22631,7 @@
         <v>81</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>120</v>
@@ -22662,7 +22660,7 @@
         <v>637</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22688,13 +22686,13 @@
         <v>138</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M165" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="M165" t="s" s="2">
+      <c r="N165" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -22702,7 +22700,7 @@
       </c>
       <c r="Q165" s="2"/>
       <c r="R165" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>79</v>
@@ -22744,7 +22742,7 @@
         <v>79</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>91</v>
@@ -22782,7 +22780,7 @@
         <v>638</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22808,10 +22806,10 @@
         <v>176</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>233</v>
+        <v>561</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -22838,7 +22836,7 @@
         <v>79</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y166" s="2"/>
       <c r="Z166" t="s" s="2">
@@ -22860,7 +22858,7 @@
         <v>79</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22869,7 +22867,7 @@
         <v>91</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>103</v>
@@ -22924,16 +22922,16 @@
         <v>154</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M167" t="s" s="2">
+      <c r="N167" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="N167" t="s" s="2">
+      <c r="O167" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>79</v>
@@ -22982,7 +22980,7 @@
         <v>79</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22991,7 +22989,7 @@
         <v>81</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ167" t="s" s="2">
         <v>103</v>
@@ -23003,10 +23001,10 @@
         <v>79</v>
       </c>
       <c r="AM167" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AN167" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AN167" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>79</v>
@@ -23046,16 +23044,16 @@
         <v>105</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M168" t="s" s="2">
+      <c r="N168" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N168" t="s" s="2">
+      <c r="O168" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>79</v>
@@ -23104,7 +23102,7 @@
         <v>79</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -23113,7 +23111,7 @@
         <v>91</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>103</v>
@@ -23125,10 +23123,10 @@
         <v>79</v>
       </c>
       <c r="AM168" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AN168" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AN168" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>79</v>
@@ -23142,7 +23140,7 @@
         <v>641</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C169" t="s" s="2">
         <v>642</v>
@@ -23167,19 +23165,19 @@
         <v>92</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L169" t="s" s="2">
         <v>643</v>
       </c>
       <c r="M169" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="N169" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="N169" t="s" s="2">
+      <c r="O169" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>79</v>
@@ -23204,7 +23202,7 @@
         <v>79</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y169" s="2"/>
       <c r="Z169" t="s" s="2">
@@ -23226,7 +23224,7 @@
         <v>79</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -23247,16 +23245,16 @@
         <v>617</v>
       </c>
       <c r="AM169" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AN169" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="AN169" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="170" hidden="true">
@@ -23264,7 +23262,7 @@
         <v>645</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23382,7 +23380,7 @@
         <v>646</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23471,7 +23469,7 @@
         <v>81</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>120</v>
@@ -23500,10 +23498,10 @@
         <v>647</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D172" t="s" s="2">
         <v>79</v>
@@ -23525,13 +23523,13 @@
         <v>79</v>
       </c>
       <c r="K172" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="L172" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="L172" t="s" s="2">
+      <c r="M172" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -23591,7 +23589,7 @@
         <v>81</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>120</v>
@@ -23620,7 +23618,7 @@
         <v>648</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23738,7 +23736,7 @@
         <v>649</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23827,7 +23825,7 @@
         <v>81</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ174" t="s" s="2">
         <v>120</v>
@@ -23856,7 +23854,7 @@
         <v>650</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23882,13 +23880,13 @@
         <v>138</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M175" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="M175" t="s" s="2">
+      <c r="N175" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -23896,7 +23894,7 @@
       </c>
       <c r="Q175" s="2"/>
       <c r="R175" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="S175" t="s" s="2">
         <v>79</v>
@@ -23938,7 +23936,7 @@
         <v>79</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>91</v>
@@ -23976,7 +23974,7 @@
         <v>651</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24002,10 +24000,10 @@
         <v>176</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>233</v>
+        <v>561</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -24032,7 +24030,7 @@
         <v>79</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
@@ -24054,7 +24052,7 @@
         <v>79</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -24063,7 +24061,7 @@
         <v>91</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>103</v>
@@ -24118,16 +24116,16 @@
         <v>154</v>
       </c>
       <c r="L177" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M177" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M177" t="s" s="2">
+      <c r="N177" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="N177" t="s" s="2">
+      <c r="O177" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>79</v>
@@ -24176,7 +24174,7 @@
         <v>79</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -24185,7 +24183,7 @@
         <v>81</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ177" t="s" s="2">
         <v>103</v>
@@ -24197,10 +24195,10 @@
         <v>79</v>
       </c>
       <c r="AM177" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AN177" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AN177" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>79</v>
@@ -24240,16 +24238,16 @@
         <v>105</v>
       </c>
       <c r="L178" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M178" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M178" t="s" s="2">
+      <c r="N178" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N178" t="s" s="2">
+      <c r="O178" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>79</v>
@@ -24298,7 +24296,7 @@
         <v>79</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -24307,7 +24305,7 @@
         <v>91</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ178" t="s" s="2">
         <v>103</v>
@@ -24319,10 +24317,10 @@
         <v>79</v>
       </c>
       <c r="AM178" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AN178" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AN178" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>79</v>
@@ -24336,7 +24334,7 @@
         <v>654</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C179" t="s" s="2">
         <v>655</v>
@@ -24361,19 +24359,19 @@
         <v>92</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L179" t="s" s="2">
         <v>656</v>
       </c>
       <c r="M179" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="N179" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="N179" t="s" s="2">
+      <c r="O179" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>79</v>
@@ -24401,11 +24399,11 @@
         <v>166</v>
       </c>
       <c r="Y179" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="Z179" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="Z179" t="s" s="2">
-        <v>535</v>
-      </c>
       <c r="AA179" t="s" s="2">
         <v>79</v>
       </c>
@@ -24422,7 +24420,7 @@
         <v>79</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -24443,16 +24441,16 @@
         <v>79</v>
       </c>
       <c r="AM179" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AN179" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="AN179" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP179" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="180" hidden="true">
@@ -24460,7 +24458,7 @@
         <v>657</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24578,7 +24576,7 @@
         <v>658</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24667,7 +24665,7 @@
         <v>81</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>120</v>
@@ -24696,10 +24694,10 @@
         <v>659</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>79</v>
@@ -24721,13 +24719,13 @@
         <v>79</v>
       </c>
       <c r="K182" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="L182" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="L182" t="s" s="2">
+      <c r="M182" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="M182" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -24787,7 +24785,7 @@
         <v>81</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>120</v>
@@ -24816,7 +24814,7 @@
         <v>660</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24934,7 +24932,7 @@
         <v>661</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25023,7 +25021,7 @@
         <v>81</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>120</v>
@@ -25052,7 +25050,7 @@
         <v>662</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25078,13 +25076,13 @@
         <v>138</v>
       </c>
       <c r="L185" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M185" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="M185" t="s" s="2">
+      <c r="N185" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -25092,7 +25090,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>79</v>
@@ -25134,7 +25132,7 @@
         <v>79</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>91</v>
@@ -25172,7 +25170,7 @@
         <v>663</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25198,10 +25196,10 @@
         <v>176</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>233</v>
+        <v>561</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -25228,7 +25226,7 @@
         <v>79</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y186" s="2"/>
       <c r="Z186" t="s" s="2">
@@ -25250,7 +25248,7 @@
         <v>79</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -25259,7 +25257,7 @@
         <v>91</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>103</v>
@@ -25314,16 +25312,16 @@
         <v>154</v>
       </c>
       <c r="L187" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M187" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M187" t="s" s="2">
+      <c r="N187" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="N187" t="s" s="2">
+      <c r="O187" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>79</v>
@@ -25372,7 +25370,7 @@
         <v>79</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -25381,7 +25379,7 @@
         <v>81</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>103</v>
@@ -25393,10 +25391,10 @@
         <v>79</v>
       </c>
       <c r="AM187" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AN187" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AN187" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>79</v>
@@ -25436,16 +25434,16 @@
         <v>105</v>
       </c>
       <c r="L188" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M188" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M188" t="s" s="2">
+      <c r="N188" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N188" t="s" s="2">
+      <c r="O188" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="O188" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>79</v>
@@ -25494,7 +25492,7 @@
         <v>79</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -25503,7 +25501,7 @@
         <v>91</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ188" t="s" s="2">
         <v>103</v>
@@ -25515,10 +25513,10 @@
         <v>79</v>
       </c>
       <c r="AM188" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AN188" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AN188" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>79</v>
@@ -25625,7 +25623,7 @@
         <v>91</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>103</v>
@@ -26310,7 +26308,7 @@
         <v>79</v>
       </c>
       <c r="X195" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y195" t="s" s="2">
         <v>705</v>
@@ -26483,7 +26481,7 @@
         <v>719</v>
       </c>
       <c r="AO196" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AP196" t="s" s="2">
         <v>79</v>
@@ -26554,7 +26552,7 @@
         <v>79</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y197" t="s" s="2">
         <v>725</v>
@@ -26759,7 +26757,7 @@
         <v>92</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L199" t="s" s="2">
         <v>738</v>
@@ -26843,7 +26841,7 @@
         <v>741</v>
       </c>
       <c r="AO199" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AP199" t="s" s="2">
         <v>79</v>
@@ -27203,7 +27201,7 @@
         <v>79</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AN202" t="s" s="2">
         <v>764</v>
@@ -27640,7 +27638,7 @@
       </c>
       <c r="Y206" s="2"/>
       <c r="Z206" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>79</v>
@@ -27719,7 +27717,7 @@
         <v>92</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L207" t="s" s="2">
         <v>779</v>
@@ -28331,7 +28329,7 @@
         <v>115</v>
       </c>
       <c r="O212" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P212" t="s" s="2">
         <v>79</v>
@@ -28441,7 +28439,7 @@
         <v>79</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L213" t="s" s="2">
         <v>804</v>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:21:45+00:00</t>
+    <t>2024-04-18T13:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8294" uniqueCount="830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8295" uniqueCount="830">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T13:43:00+00:00</t>
+    <t>2024-04-25T11:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -692,6 +692,9 @@
 </t>
   </si>
   <si>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
     <t>The date range that this organization should be considered available.</t>
   </si>
   <si>
@@ -741,7 +744,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -781,8 +784,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>dateCreation</t>
@@ -1074,7 +1077,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="IDNST"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1306,7 +1309,7 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>http://interopsante.org/CodeSystem/fr-v2-0203</t>
+    <t>https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1451,7 +1454,7 @@
     <t>Organization.identifier:sirene.system</t>
   </si>
   <si>
-    <t>http://sirene.fr</t>
+    <t>https://sirene.fr</t>
   </si>
   <si>
     <t>Organization.identifier:sirene.value</t>
@@ -1529,7 +1532,7 @@
     <t>Organization.identifier:finess.system</t>
   </si>
   <si>
-    <t>http://finess.esante.gouv.fr</t>
+    <t>https://finess.esante.gouv.fr</t>
   </si>
   <si>
     <t>Organization.identifier:finess.value</t>
@@ -1564,7 +1567,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="INTRN"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1758,9 +1761,6 @@
   </si>
   <si>
     <t>Organization.type.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-organization-types</t>
@@ -5504,10 +5504,10 @@
         <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5582,7 +5582,7 @@
         <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>79</v>
@@ -5593,10 +5593,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5711,14 +5711,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5740,12 +5740,14 @@
         <v>112</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>201</v>
+        <v>113</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -5803,7 +5805,7 @@
         <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>120</v>
@@ -5818,7 +5820,7 @@
         <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -5829,10 +5831,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5858,13 +5860,13 @@
         <v>138</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5872,7 +5874,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>79</v>
@@ -5914,7 +5916,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>91</v>
@@ -5949,10 +5951,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5975,13 +5977,13 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -6032,7 +6034,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -6041,7 +6043,7 @@
         <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>103</v>
@@ -6067,10 +6069,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6185,10 +6187,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6279,7 +6281,7 @@
         <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>120</v>
@@ -6294,7 +6296,7 @@
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -6305,10 +6307,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6331,16 +6333,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6390,7 +6392,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -6399,22 +6401,22 @@
         <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -6425,10 +6427,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6451,23 +6453,23 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="R30" t="s" s="2">
         <v>79</v>
@@ -6512,7 +6514,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6521,22 +6523,22 @@
         <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -6547,13 +6549,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>79</v>
@@ -6575,13 +6577,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6667,13 +6669,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>79</v>
@@ -6695,13 +6697,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6767,7 +6769,7 @@
         <v>120</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>79</v>
@@ -6787,13 +6789,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>79</v>
@@ -6815,13 +6817,13 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6890,7 +6892,7 @@
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
@@ -6907,13 +6909,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>79</v>
@@ -6935,13 +6937,13 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -7007,10 +7009,10 @@
         <v>120</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
@@ -7027,13 +7029,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>79</v>
@@ -7055,13 +7057,13 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -7130,7 +7132,7 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
@@ -7147,13 +7149,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>79</v>
@@ -7175,13 +7177,13 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -7267,10 +7269,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7296,16 +7298,16 @@
         <v>112</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -7354,7 +7356,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -7389,10 +7391,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7415,17 +7417,17 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -7462,10 +7464,10 @@
         <v>79</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>79</v>
@@ -7474,7 +7476,7 @@
         <v>118</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7483,7 +7485,7 @@
         <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>103</v>
@@ -7495,27 +7497,27 @@
         <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>79</v>
@@ -7537,17 +7539,17 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -7596,7 +7598,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7605,36 +7607,36 @@
         <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7749,10 +7751,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7869,10 +7871,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7898,16 +7900,16 @@
         <v>176</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -7917,7 +7919,7 @@
         <v>79</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>79</v>
@@ -7932,13 +7934,13 @@
         <v>79</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>79</v>
@@ -7956,7 +7958,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7980,7 +7982,7 @@
         <v>199</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -7991,10 +7993,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8017,19 +8019,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -8039,7 +8041,7 @@
         <v>79</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>79</v>
@@ -8057,10 +8059,10 @@
         <v>158</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -8078,7 +8080,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -8099,10 +8101,10 @@
         <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -8113,10 +8115,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8142,16 +8144,16 @@
         <v>138</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -8161,10 +8163,10 @@
         <v>79</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>79</v>
@@ -8200,7 +8202,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -8221,13 +8223,13 @@
         <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -8235,10 +8237,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8264,13 +8266,13 @@
         <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8284,7 +8286,7 @@
         <v>79</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>79</v>
@@ -8320,7 +8322,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -8341,13 +8343,13 @@
         <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>79</v>
@@ -8355,10 +8357,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8381,13 +8383,13 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8438,7 +8440,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8459,13 +8461,13 @@
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>79</v>
@@ -8473,10 +8475,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8499,16 +8501,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8558,7 +8560,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8579,13 +8581,13 @@
         <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>79</v>
@@ -8593,13 +8595,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>79</v>
@@ -8621,17 +8623,17 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -8680,7 +8682,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8689,36 +8691,36 @@
         <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8833,10 +8835,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8953,10 +8955,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8982,16 +8984,16 @@
         <v>176</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -9016,13 +9018,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -9040,7 +9042,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -9064,7 +9066,7 @@
         <v>199</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -9075,10 +9077,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9101,19 +9103,19 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -9141,10 +9143,10 @@
         <v>158</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -9162,7 +9164,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -9183,10 +9185,10 @@
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -9197,10 +9199,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9315,10 +9317,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9435,10 +9437,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9464,16 +9466,16 @@
         <v>154</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -9522,7 +9524,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9543,10 +9545,10 @@
         <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -9557,10 +9559,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9675,10 +9677,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9795,10 +9797,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9824,16 +9826,16 @@
         <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -9843,7 +9845,7 @@
         <v>79</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>79</v>
@@ -9882,7 +9884,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9903,10 +9905,10 @@
         <v>79</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -9917,10 +9919,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9946,13 +9948,13 @@
         <v>105</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10002,7 +10004,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -10023,10 +10025,10 @@
         <v>79</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -10037,10 +10039,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10066,14 +10068,14 @@
         <v>176</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -10122,7 +10124,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -10143,10 +10145,10 @@
         <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -10157,10 +10159,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10186,14 +10188,14 @@
         <v>105</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -10242,7 +10244,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -10263,10 +10265,10 @@
         <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -10277,10 +10279,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10303,19 +10305,19 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
@@ -10364,7 +10366,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10385,10 +10387,10 @@
         <v>79</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -10399,10 +10401,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10428,16 +10430,16 @@
         <v>105</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -10486,7 +10488,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10507,10 +10509,10 @@
         <v>79</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -10521,10 +10523,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10550,16 +10552,16 @@
         <v>138</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -10569,10 +10571,10 @@
         <v>79</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>79</v>
@@ -10608,7 +10610,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10629,13 +10631,13 @@
         <v>79</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>79</v>
@@ -10643,10 +10645,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10672,13 +10674,13 @@
         <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10692,7 +10694,7 @@
         <v>79</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>79</v>
@@ -10728,7 +10730,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10749,13 +10751,13 @@
         <v>79</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>79</v>
@@ -10763,10 +10765,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10789,13 +10791,13 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10846,7 +10848,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10867,13 +10869,13 @@
         <v>79</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>79</v>
@@ -10881,10 +10883,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10907,16 +10909,16 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10966,7 +10968,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10987,13 +10989,13 @@
         <v>79</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>79</v>
@@ -11001,13 +11003,13 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>79</v>
@@ -11029,17 +11031,17 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -11088,7 +11090,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -11097,36 +11099,36 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11241,10 +11243,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11361,10 +11363,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11390,16 +11392,16 @@
         <v>176</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -11424,13 +11426,13 @@
         <v>79</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>79</v>
@@ -11448,7 +11450,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11472,7 +11474,7 @@
         <v>199</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -11483,10 +11485,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11509,19 +11511,19 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
@@ -11549,10 +11551,10 @@
         <v>158</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>79</v>
@@ -11570,7 +11572,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11591,10 +11593,10 @@
         <v>79</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -11605,10 +11607,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11723,10 +11725,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11843,10 +11845,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11872,16 +11874,16 @@
         <v>154</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -11930,7 +11932,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11951,10 +11953,10 @@
         <v>79</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>79</v>
@@ -11965,10 +11967,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12083,10 +12085,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12203,10 +12205,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12232,16 +12234,16 @@
         <v>138</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>79</v>
@@ -12251,7 +12253,7 @@
         <v>79</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>79</v>
@@ -12290,7 +12292,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12311,10 +12313,10 @@
         <v>79</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>79</v>
@@ -12325,10 +12327,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12354,13 +12356,13 @@
         <v>105</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12410,7 +12412,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12431,10 +12433,10 @@
         <v>79</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>79</v>
@@ -12445,10 +12447,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12474,14 +12476,14 @@
         <v>176</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>79</v>
@@ -12530,7 +12532,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12551,10 +12553,10 @@
         <v>79</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>79</v>
@@ -12565,10 +12567,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12594,14 +12596,14 @@
         <v>105</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>79</v>
@@ -12650,7 +12652,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12671,10 +12673,10 @@
         <v>79</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>79</v>
@@ -12685,10 +12687,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12711,19 +12713,19 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>79</v>
@@ -12772,7 +12774,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12793,10 +12795,10 @@
         <v>79</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>79</v>
@@ -12807,10 +12809,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12836,16 +12838,16 @@
         <v>105</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>79</v>
@@ -12894,7 +12896,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12915,10 +12917,10 @@
         <v>79</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>79</v>
@@ -12929,10 +12931,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12958,16 +12960,16 @@
         <v>138</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>79</v>
@@ -12977,10 +12979,10 @@
         <v>79</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>79</v>
@@ -13016,7 +13018,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -13037,13 +13039,13 @@
         <v>79</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>79</v>
@@ -13051,10 +13053,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13080,13 +13082,13 @@
         <v>105</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -13100,7 +13102,7 @@
         <v>79</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>79</v>
@@ -13136,7 +13138,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -13157,13 +13159,13 @@
         <v>79</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>79</v>
@@ -13171,10 +13173,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13197,13 +13199,13 @@
         <v>92</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13254,7 +13256,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13275,13 +13277,13 @@
         <v>79</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>79</v>
@@ -13289,10 +13291,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13315,16 +13317,16 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13374,7 +13376,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13395,13 +13397,13 @@
         <v>79</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>79</v>
@@ -13409,13 +13411,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>79</v>
@@ -13437,17 +13439,17 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>79</v>
@@ -13496,7 +13498,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13505,7 +13507,7 @@
         <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>103</v>
@@ -13517,24 +13519,24 @@
         <v>79</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13649,10 +13651,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13769,10 +13771,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13798,16 +13800,16 @@
         <v>176</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -13832,13 +13834,13 @@
         <v>79</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>79</v>
@@ -13856,7 +13858,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13880,7 +13882,7 @@
         <v>199</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>79</v>
@@ -13891,10 +13893,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13917,19 +13919,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -13939,7 +13941,7 @@
         <v>79</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>79</v>
@@ -13957,10 +13959,10 @@
         <v>158</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>79</v>
@@ -13978,7 +13980,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13999,10 +14001,10 @@
         <v>79</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>79</v>
@@ -14013,10 +14015,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14042,16 +14044,16 @@
         <v>138</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>79</v>
@@ -14061,10 +14063,10 @@
         <v>79</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>79</v>
@@ -14100,7 +14102,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -14121,13 +14123,13 @@
         <v>79</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>79</v>
@@ -14135,10 +14137,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14164,13 +14166,13 @@
         <v>105</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14184,7 +14186,7 @@
         <v>79</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>79</v>
@@ -14220,7 +14222,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14241,13 +14243,13 @@
         <v>79</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>79</v>
@@ -14255,10 +14257,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14281,13 +14283,13 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14338,7 +14340,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14359,13 +14361,13 @@
         <v>79</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>79</v>
@@ -14373,10 +14375,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14399,16 +14401,16 @@
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14458,7 +14460,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14479,13 +14481,13 @@
         <v>79</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>79</v>
@@ -14493,13 +14495,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>79</v>
@@ -14521,17 +14523,17 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>79</v>
@@ -14580,7 +14582,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14589,7 +14591,7 @@
         <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>103</v>
@@ -14601,24 +14603,24 @@
         <v>79</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14733,10 +14735,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14853,10 +14855,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14882,16 +14884,16 @@
         <v>176</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>79</v>
@@ -14916,13 +14918,13 @@
         <v>79</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>79</v>
@@ -14940,7 +14942,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14964,7 +14966,7 @@
         <v>199</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>79</v>
@@ -14975,10 +14977,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15001,19 +15003,19 @@
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>79</v>
@@ -15023,7 +15025,7 @@
         <v>79</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>79</v>
@@ -15041,10 +15043,10 @@
         <v>158</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>79</v>
@@ -15062,7 +15064,7 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -15083,10 +15085,10 @@
         <v>79</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>79</v>
@@ -15097,10 +15099,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15126,16 +15128,16 @@
         <v>138</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>79</v>
@@ -15145,10 +15147,10 @@
         <v>79</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="T102" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U102" t="s" s="2">
         <v>79</v>
@@ -15184,7 +15186,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -15205,13 +15207,13 @@
         <v>79</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>79</v>
@@ -15219,10 +15221,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15248,13 +15250,13 @@
         <v>105</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -15268,7 +15270,7 @@
         <v>79</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>79</v>
@@ -15304,7 +15306,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15325,13 +15327,13 @@
         <v>79</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>79</v>
@@ -15339,10 +15341,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15365,13 +15367,13 @@
         <v>92</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15422,7 +15424,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15443,13 +15445,13 @@
         <v>79</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>79</v>
@@ -15457,10 +15459,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15483,16 +15485,16 @@
         <v>92</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15542,7 +15544,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15563,13 +15565,13 @@
         <v>79</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>79</v>
@@ -15577,10 +15579,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15603,70 +15605,70 @@
         <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q106" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="R106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF106" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="P106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q106" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="R106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15684,27 +15686,27 @@
         <v>79</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15727,19 +15729,19 @@
         <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>79</v>
@@ -15767,16 +15769,16 @@
         <v>166</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
@@ -15786,7 +15788,7 @@
         <v>118</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15807,27 +15809,27 @@
         <v>79</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>79</v>
@@ -15849,19 +15851,19 @@
         <v>92</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>79</v>
@@ -15886,11 +15888,11 @@
         <v>79</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>79</v>
@@ -15908,7 +15910,7 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15929,24 +15931,24 @@
         <v>79</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16061,10 +16063,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16179,13 +16181,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="B111" t="s" s="2">
-        <v>546</v>
-      </c>
       <c r="C111" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>79</v>
@@ -16207,13 +16209,13 @@
         <v>79</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16299,10 +16301,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16417,10 +16419,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16509,7 +16511,7 @@
         <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>120</v>
@@ -16535,10 +16537,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16564,13 +16566,13 @@
         <v>138</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16578,7 +16580,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>79</v>
@@ -16620,7 +16622,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>91</v>
@@ -16655,10 +16657,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16684,10 +16686,10 @@
         <v>176</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>561</v>
+        <v>233</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16699,7 +16701,7 @@
         <v>79</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>79</v>
@@ -16714,7 +16716,7 @@
         <v>79</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
@@ -16736,7 +16738,7 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16745,7 +16747,7 @@
         <v>91</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>103</v>
@@ -16800,16 +16802,16 @@
         <v>154</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>79</v>
@@ -16858,7 +16860,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16879,10 +16881,10 @@
         <v>79</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>79</v>
@@ -17160,16 +17162,16 @@
         <v>138</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -17218,7 +17220,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -17239,10 +17241,10 @@
         <v>79</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>79</v>
@@ -17282,13 +17284,13 @@
         <v>105</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17338,7 +17340,7 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17359,10 +17361,10 @@
         <v>79</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>79</v>
@@ -17405,11 +17407,11 @@
         <v>575</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>79</v>
@@ -17458,7 +17460,7 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17479,10 +17481,10 @@
         <v>79</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>79</v>
@@ -17522,14 +17524,14 @@
         <v>105</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>79</v>
@@ -17578,7 +17580,7 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17599,10 +17601,10 @@
         <v>79</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>79</v>
@@ -17639,19 +17641,19 @@
         <v>92</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>79</v>
@@ -17700,7 +17702,7 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17721,10 +17723,10 @@
         <v>79</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>79</v>
@@ -17764,16 +17766,16 @@
         <v>105</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>79</v>
@@ -17822,7 +17824,7 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17843,10 +17845,10 @@
         <v>79</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>79</v>
@@ -17860,7 +17862,7 @@
         <v>582</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C125" t="s" s="2">
         <v>583</v>
@@ -17885,19 +17887,19 @@
         <v>92</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L125" t="s" s="2">
         <v>584</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>79</v>
@@ -17922,7 +17924,7 @@
         <v>79</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
@@ -17944,7 +17946,7 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17965,16 +17967,16 @@
         <v>79</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="126" hidden="true">
@@ -17982,7 +17984,7 @@
         <v>586</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18100,7 +18102,7 @@
         <v>587</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18246,16 +18248,16 @@
         <v>154</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>79</v>
@@ -18304,7 +18306,7 @@
         <v>79</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18325,10 +18327,10 @@
         <v>79</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>79</v>
@@ -18606,16 +18608,16 @@
         <v>138</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>79</v>
@@ -18664,7 +18666,7 @@
         <v>79</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18685,10 +18687,10 @@
         <v>79</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>79</v>
@@ -18728,13 +18730,13 @@
         <v>105</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18784,7 +18786,7 @@
         <v>79</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18805,10 +18807,10 @@
         <v>79</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>79</v>
@@ -18851,11 +18853,11 @@
         <v>575</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>79</v>
@@ -18904,7 +18906,7 @@
         <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18925,10 +18927,10 @@
         <v>79</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>79</v>
@@ -18968,14 +18970,14 @@
         <v>105</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>79</v>
@@ -19024,7 +19026,7 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -19045,10 +19047,10 @@
         <v>79</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>79</v>
@@ -19085,19 +19087,19 @@
         <v>92</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>79</v>
@@ -19146,7 +19148,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -19167,10 +19169,10 @@
         <v>79</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>79</v>
@@ -19210,16 +19212,16 @@
         <v>105</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>79</v>
@@ -19268,7 +19270,7 @@
         <v>79</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -19289,10 +19291,10 @@
         <v>79</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>79</v>
@@ -19306,7 +19308,7 @@
         <v>597</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C137" t="s" s="2">
         <v>598</v>
@@ -19331,19 +19333,19 @@
         <v>92</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L137" t="s" s="2">
         <v>599</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>79</v>
@@ -19368,7 +19370,7 @@
         <v>79</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
@@ -19390,7 +19392,7 @@
         <v>79</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19411,16 +19413,16 @@
         <v>79</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="138" hidden="true">
@@ -19428,7 +19430,7 @@
         <v>601</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19546,7 +19548,7 @@
         <v>602</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19692,16 +19694,16 @@
         <v>154</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>79</v>
@@ -19750,7 +19752,7 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19771,10 +19773,10 @@
         <v>79</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>79</v>
@@ -20052,16 +20054,16 @@
         <v>138</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>79</v>
@@ -20110,7 +20112,7 @@
         <v>79</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -20131,10 +20133,10 @@
         <v>79</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>79</v>
@@ -20174,13 +20176,13 @@
         <v>105</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -20230,7 +20232,7 @@
         <v>79</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -20251,10 +20253,10 @@
         <v>79</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>79</v>
@@ -20297,11 +20299,11 @@
         <v>575</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>79</v>
@@ -20350,7 +20352,7 @@
         <v>79</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20371,10 +20373,10 @@
         <v>79</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>79</v>
@@ -20414,14 +20416,14 @@
         <v>105</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>79</v>
@@ -20470,7 +20472,7 @@
         <v>79</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20491,10 +20493,10 @@
         <v>79</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>79</v>
@@ -20531,19 +20533,19 @@
         <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>79</v>
@@ -20592,7 +20594,7 @@
         <v>79</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20613,10 +20615,10 @@
         <v>79</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>79</v>
@@ -20656,16 +20658,16 @@
         <v>105</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>79</v>
@@ -20714,7 +20716,7 @@
         <v>79</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20735,10 +20737,10 @@
         <v>79</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>79</v>
@@ -20752,7 +20754,7 @@
         <v>612</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C149" t="s" s="2">
         <v>613</v>
@@ -20777,19 +20779,19 @@
         <v>92</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L149" t="s" s="2">
         <v>614</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>79</v>
@@ -20814,7 +20816,7 @@
         <v>79</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
@@ -20836,7 +20838,7 @@
         <v>79</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20857,16 +20859,16 @@
         <v>617</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="150" hidden="true">
@@ -20874,7 +20876,7 @@
         <v>618</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20992,7 +20994,7 @@
         <v>619</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21081,7 +21083,7 @@
         <v>81</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>120</v>
@@ -21110,10 +21112,10 @@
         <v>620</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>79</v>
@@ -21135,13 +21137,13 @@
         <v>79</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21201,7 +21203,7 @@
         <v>81</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>120</v>
@@ -21230,7 +21232,7 @@
         <v>621</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21348,7 +21350,7 @@
         <v>622</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21437,7 +21439,7 @@
         <v>81</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>120</v>
@@ -21466,7 +21468,7 @@
         <v>623</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21492,13 +21494,13 @@
         <v>138</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21506,7 +21508,7 @@
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>79</v>
@@ -21548,7 +21550,7 @@
         <v>79</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>91</v>
@@ -21586,7 +21588,7 @@
         <v>624</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21612,10 +21614,10 @@
         <v>176</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>561</v>
+        <v>233</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21642,7 +21644,7 @@
         <v>79</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
@@ -21664,7 +21666,7 @@
         <v>79</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21673,7 +21675,7 @@
         <v>91</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ156" t="s" s="2">
         <v>103</v>
@@ -21728,16 +21730,16 @@
         <v>154</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>79</v>
@@ -21786,7 +21788,7 @@
         <v>79</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21795,7 +21797,7 @@
         <v>81</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>103</v>
@@ -21807,10 +21809,10 @@
         <v>79</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>79</v>
@@ -21850,16 +21852,16 @@
         <v>105</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>79</v>
@@ -21908,7 +21910,7 @@
         <v>79</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21917,7 +21919,7 @@
         <v>91</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>103</v>
@@ -21929,10 +21931,10 @@
         <v>79</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>79</v>
@@ -21946,7 +21948,7 @@
         <v>627</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C159" t="s" s="2">
         <v>628</v>
@@ -21971,19 +21973,19 @@
         <v>92</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L159" t="s" s="2">
         <v>629</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>79</v>
@@ -22008,7 +22010,7 @@
         <v>79</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y159" s="2"/>
       <c r="Z159" t="s" s="2">
@@ -22030,7 +22032,7 @@
         <v>79</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -22051,16 +22053,16 @@
         <v>79</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="160" hidden="true">
@@ -22068,7 +22070,7 @@
         <v>632</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22186,7 +22188,7 @@
         <v>633</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22275,7 +22277,7 @@
         <v>81</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>120</v>
@@ -22304,10 +22306,10 @@
         <v>634</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D162" t="s" s="2">
         <v>79</v>
@@ -22329,13 +22331,13 @@
         <v>79</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -22395,7 +22397,7 @@
         <v>81</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>120</v>
@@ -22424,7 +22426,7 @@
         <v>635</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22542,7 +22544,7 @@
         <v>636</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22631,7 +22633,7 @@
         <v>81</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>120</v>
@@ -22660,7 +22662,7 @@
         <v>637</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22686,13 +22688,13 @@
         <v>138</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -22700,7 +22702,7 @@
       </c>
       <c r="Q165" s="2"/>
       <c r="R165" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>79</v>
@@ -22742,7 +22744,7 @@
         <v>79</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>91</v>
@@ -22780,7 +22782,7 @@
         <v>638</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22806,10 +22808,10 @@
         <v>176</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>561</v>
+        <v>233</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -22836,7 +22838,7 @@
         <v>79</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y166" s="2"/>
       <c r="Z166" t="s" s="2">
@@ -22858,7 +22860,7 @@
         <v>79</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22867,7 +22869,7 @@
         <v>91</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>103</v>
@@ -22922,16 +22924,16 @@
         <v>154</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>79</v>
@@ -22980,7 +22982,7 @@
         <v>79</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22989,7 +22991,7 @@
         <v>81</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ167" t="s" s="2">
         <v>103</v>
@@ -23001,10 +23003,10 @@
         <v>79</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>79</v>
@@ -23044,16 +23046,16 @@
         <v>105</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>79</v>
@@ -23102,7 +23104,7 @@
         <v>79</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -23111,7 +23113,7 @@
         <v>91</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>103</v>
@@ -23123,10 +23125,10 @@
         <v>79</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>79</v>
@@ -23140,7 +23142,7 @@
         <v>641</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C169" t="s" s="2">
         <v>642</v>
@@ -23165,19 +23167,19 @@
         <v>92</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L169" t="s" s="2">
         <v>643</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>79</v>
@@ -23202,7 +23204,7 @@
         <v>79</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y169" s="2"/>
       <c r="Z169" t="s" s="2">
@@ -23224,7 +23226,7 @@
         <v>79</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -23245,16 +23247,16 @@
         <v>617</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="170" hidden="true">
@@ -23262,7 +23264,7 @@
         <v>645</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23380,7 +23382,7 @@
         <v>646</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23469,7 +23471,7 @@
         <v>81</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>120</v>
@@ -23498,10 +23500,10 @@
         <v>647</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D172" t="s" s="2">
         <v>79</v>
@@ -23523,13 +23525,13 @@
         <v>79</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -23589,7 +23591,7 @@
         <v>81</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>120</v>
@@ -23618,7 +23620,7 @@
         <v>648</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23736,7 +23738,7 @@
         <v>649</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23825,7 +23827,7 @@
         <v>81</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ174" t="s" s="2">
         <v>120</v>
@@ -23854,7 +23856,7 @@
         <v>650</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23880,13 +23882,13 @@
         <v>138</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -23894,7 +23896,7 @@
       </c>
       <c r="Q175" s="2"/>
       <c r="R175" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S175" t="s" s="2">
         <v>79</v>
@@ -23936,7 +23938,7 @@
         <v>79</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>91</v>
@@ -23974,7 +23976,7 @@
         <v>651</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24000,10 +24002,10 @@
         <v>176</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>561</v>
+        <v>233</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -24030,7 +24032,7 @@
         <v>79</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
@@ -24052,7 +24054,7 @@
         <v>79</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -24061,7 +24063,7 @@
         <v>91</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>103</v>
@@ -24116,16 +24118,16 @@
         <v>154</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>79</v>
@@ -24174,7 +24176,7 @@
         <v>79</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -24183,7 +24185,7 @@
         <v>81</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ177" t="s" s="2">
         <v>103</v>
@@ -24195,10 +24197,10 @@
         <v>79</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>79</v>
@@ -24238,16 +24240,16 @@
         <v>105</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>79</v>
@@ -24296,7 +24298,7 @@
         <v>79</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -24305,7 +24307,7 @@
         <v>91</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ178" t="s" s="2">
         <v>103</v>
@@ -24317,10 +24319,10 @@
         <v>79</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>79</v>
@@ -24334,7 +24336,7 @@
         <v>654</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C179" t="s" s="2">
         <v>655</v>
@@ -24359,19 +24361,19 @@
         <v>92</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L179" t="s" s="2">
         <v>656</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>79</v>
@@ -24399,10 +24401,10 @@
         <v>166</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>79</v>
@@ -24420,7 +24422,7 @@
         <v>79</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -24441,16 +24443,16 @@
         <v>79</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP179" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="180" hidden="true">
@@ -24458,7 +24460,7 @@
         <v>657</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24576,7 +24578,7 @@
         <v>658</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24665,7 +24667,7 @@
         <v>81</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>120</v>
@@ -24694,10 +24696,10 @@
         <v>659</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>79</v>
@@ -24719,13 +24721,13 @@
         <v>79</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -24785,7 +24787,7 @@
         <v>81</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>120</v>
@@ -24814,7 +24816,7 @@
         <v>660</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24932,7 +24934,7 @@
         <v>661</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25021,7 +25023,7 @@
         <v>81</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>120</v>
@@ -25050,7 +25052,7 @@
         <v>662</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25076,13 +25078,13 @@
         <v>138</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -25090,7 +25092,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>79</v>
@@ -25132,7 +25134,7 @@
         <v>79</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>91</v>
@@ -25170,7 +25172,7 @@
         <v>663</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25196,10 +25198,10 @@
         <v>176</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>561</v>
+        <v>233</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -25226,7 +25228,7 @@
         <v>79</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y186" s="2"/>
       <c r="Z186" t="s" s="2">
@@ -25248,7 +25250,7 @@
         <v>79</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -25257,7 +25259,7 @@
         <v>91</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>103</v>
@@ -25312,16 +25314,16 @@
         <v>154</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>79</v>
@@ -25370,7 +25372,7 @@
         <v>79</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -25379,7 +25381,7 @@
         <v>81</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>103</v>
@@ -25391,10 +25393,10 @@
         <v>79</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>79</v>
@@ -25434,16 +25436,16 @@
         <v>105</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>79</v>
@@ -25492,7 +25494,7 @@
         <v>79</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -25501,7 +25503,7 @@
         <v>91</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ188" t="s" s="2">
         <v>103</v>
@@ -25513,10 +25515,10 @@
         <v>79</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>79</v>
@@ -25623,7 +25625,7 @@
         <v>91</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>103</v>
@@ -26308,7 +26310,7 @@
         <v>79</v>
       </c>
       <c r="X195" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y195" t="s" s="2">
         <v>705</v>
@@ -26481,7 +26483,7 @@
         <v>719</v>
       </c>
       <c r="AO196" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP196" t="s" s="2">
         <v>79</v>
@@ -26552,7 +26554,7 @@
         <v>79</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y197" t="s" s="2">
         <v>725</v>
@@ -26757,7 +26759,7 @@
         <v>92</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L199" t="s" s="2">
         <v>738</v>
@@ -26841,7 +26843,7 @@
         <v>741</v>
       </c>
       <c r="AO199" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP199" t="s" s="2">
         <v>79</v>
@@ -27201,7 +27203,7 @@
         <v>79</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN202" t="s" s="2">
         <v>764</v>
@@ -27638,7 +27640,7 @@
       </c>
       <c r="Y206" s="2"/>
       <c r="Z206" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>79</v>
@@ -27717,7 +27719,7 @@
         <v>92</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L207" t="s" s="2">
         <v>779</v>
@@ -28329,7 +28331,7 @@
         <v>115</v>
       </c>
       <c r="O212" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P212" t="s" s="2">
         <v>79</v>
@@ -28439,7 +28441,7 @@
         <v>79</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L213" t="s" s="2">
         <v>804</v>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:10:14+00:00</t>
+    <t>2024-06-03T16:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:22:01+00:00</t>
+    <t>2024-06-03T16:23:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:23:50+00:00</t>
+    <t>2024-06-03T16:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:30:34+00:00</t>
+    <t>2024-06-05T12:07:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T12:07:44+00:00</t>
+    <t>2024-06-07T15:57:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-07T15:57:22+00:00</t>
+    <t>2024-07-01T19:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:46:33+00:00</t>
+    <t>2024-07-09T08:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T09:54:14+00:00</t>
+    <t>2024-07-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:00:25+00:00</t>
+    <t>2024-07-10T10:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:02:38+00:00</t>
+    <t>2024-07-10T10:13:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:13:33+00:00</t>
+    <t>2024-07-10T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:01:49+00:00</t>
+    <t>2024-07-10T12:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:37:24+00:00</t>
+    <t>2024-07-10T13:09:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:17+00:00</t>
+    <t>2024-07-10T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:58+00:00</t>
+    <t>2024-07-10T13:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:27:13+00:00</t>
+    <t>2024-07-11T14:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:15:05+00:00</t>
+    <t>2024-07-11T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:32:47+00:00</t>
+    <t>2024-07-11T15:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:43:40+00:00</t>
+    <t>2024-07-11T16:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T16:04:15+00:00</t>
+    <t>2024-07-12T06:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T06:54:28+00:00</t>
+    <t>2024-07-12T07:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T17:01:01+00:00</t>
+    <t>2025-01-31T09:33:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T09:33:18+00:00</t>
+    <t>2025-02-03T16:26:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:26:04+00:00</t>
+    <t>2025-02-11T12:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:19:13+00:00</t>
+    <t>2025-02-11T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:46:26+00:00</t>
+    <t>2025-02-11T13:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:37:59+00:00</t>
+    <t>2025-02-11T14:09:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T14:09:44+00:00</t>
+    <t>2025-02-11T15:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:57:50+00:00</t>
+    <t>2025-02-11T16:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:04:30+00:00</t>
+    <t>2025-02-11T16:35:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T22:39:20+00:00</t>
+    <t>2025-02-24T08:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T08:37:03+00:00</t>
+    <t>2025-02-27T14:21:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:21:41+00:00</t>
+    <t>2025-02-27T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:23:05+00:00</t>
+    <t>2025-02-28T10:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:02:48+00:00</t>
+    <t>2025-03-05T17:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T17:59:44+00:00</t>
+    <t>2025-03-06T14:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:41:30+00:00</t>
+    <t>2025-03-06T14:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:56:25+00:00</t>
+    <t>2025-03-12T15:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T15:24:25+00:00</t>
+    <t>2025-03-18T14:02:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:02:39+00:00</t>
+    <t>2025-03-18T16:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T16:59:29+00:00</t>
+    <t>2025-03-21T10:50:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:53:04+00:00</t>
+    <t>2026-06-19T14:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:07:56+00:00</t>
+    <t>2026-06-23T09:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T09:20:47+00:00</t>
+    <t>2026-06-23T12:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T12:21:55+00:00</t>
+    <t>2026-06-26T10:36:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:36:05+00:00</t>
+    <t>2026-06-27T10:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-27T10:35:23+00:00</t>
+    <t>2026-06-30T07:59:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:59:11+00:00</t>
+    <t>2026-07-10T15:33:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:33:23+00:00</t>
+    <t>2026-07-10T15:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -903,7 +903,7 @@
     <t>as-ext-digital-certificate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -919,7 +919,7 @@
     <t>as-ext-organization-pharmacy-licence</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-pharmacy-licence|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-pharmacy-licence|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -938,7 +938,7 @@
     <t>as-ext-organization-pricing-model</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-pricing-model|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-pricing-model|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -957,7 +957,7 @@
     <t>as-ext-organization-closing-type</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-closing-type|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-closing-type|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -979,7 +979,7 @@
     <t>as-ext-organization-budget-type</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-budget-type|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-budget-type|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -998,7 +998,7 @@
     <t>as-ext-organization-authorization-deadline</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-authorization-deadline|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-authorization-deadline|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -1790,7 +1790,7 @@
     <t>as-ext-organization-types</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-types|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-types|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -1830,7 +1830,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-organization-types|1.2.0-snapshot-2</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-organization-types|1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Organization.type:organizationType.coding</t>
@@ -2097,7 +2097,7 @@
     <t>Le type d’établissement détermine si c'est un établissement principal ou secondaire.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-type-etablissement|1.2.0-snapshot-2</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-type-etablissement|1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>EntiteGeographique.typeEtablissement</t>
@@ -2380,7 +2380,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-2}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -2444,7 +2444,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -2606,7 +2606,7 @@
     <t>Organization.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-2}
+    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -2648,7 +2648,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-3)
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:46:03+00:00</t>
+    <t>2026-08-03T13:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:23:25+00:00</t>
+    <t>2026-08-03T14:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T14:28:09+00:00</t>
+    <t>2026-08-04T08:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-organization.xlsx
+++ b/main/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:16:57+00:00</t>
+    <t>2026-08-04T12:10:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
